--- a/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D255"/>
+  <dimension ref="A1:D313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4339,20 +4339,14 @@
           <t>tYjCfe2E</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="B245" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C245" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D245" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="246">
@@ -4361,20 +4355,14 @@
           <t>8UHsapgU</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="B246" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C246" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D246" t="n">
+        <v>2.45</v>
       </c>
     </row>
     <row r="247">
@@ -4383,20 +4371,14 @@
           <t>2meCcXHP</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="B247" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C247" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D247" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="248">
@@ -4405,20 +4387,14 @@
           <t>bJtrhBum</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
+      <c r="B248" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C248" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D248" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="249">
@@ -4427,20 +4403,14 @@
           <t>CrrhJmvn</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B249" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C249" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D249" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="250">
@@ -4449,20 +4419,14 @@
           <t>ILdqjkAa</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B250" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C250" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D250" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="251">
@@ -4471,20 +4435,14 @@
           <t>Qo0ilTvC</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="B251" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C251" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D251" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="252">
@@ -4493,20 +4451,14 @@
           <t>n1l0n79O</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
+      <c r="B252" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C252" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D252" t="n">
+        <v>2.63</v>
       </c>
     </row>
     <row r="253">
@@ -4515,20 +4467,14 @@
           <t>xQT96Aft</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="B253" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C253" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D253" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="254">
@@ -4537,20 +4483,14 @@
           <t>04EZ06OH</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="B254" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C254" t="n">
+        <v>4</v>
+      </c>
+      <c r="D254" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="255">
@@ -4559,19 +4499,1265 @@
           <t>pCQRkLbJ</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
+      <c r="B255" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C255" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D255" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>fmqtFMjD</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>8WpYGrM0</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>nHdPI4il</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>CntkHiGq</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>hdlcFVpd</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
         <is>
           <t>3.10</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr">
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>pjyqwZx3</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>tIUiyD7F</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>t4kJMDhM</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>Kl1AOZN9</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>697ha3El</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>634r8bcJ</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
         <is>
           <t>3.50</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr">
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>pbFTwdnB</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>vyoZBtbf</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>CnnJp4ae</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>bw1zAKS6</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>GINCsvmn</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>x6klsVh3</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>b3pRrrU7</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>WfkfPdXH</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>SMr3Nz2U</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>xYBLuIHb</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>6os5wmhS</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>Kl7vhn7L</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>nw6fJO5K</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>bHPacsq1</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>MwmHgKaN</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>lQl9etVA</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>KWD8eLDD</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>xUXzYQFk</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
         <is>
           <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>CCV9JR0d</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>bsinRI25</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>GbaVU03t</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>tOTmlbNp</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>nPQL4PjR</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>pWhdu9NF</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>6NnRD2Ts</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>2FcwTvYh</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>EBSD6oME</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>WSQqW4p2</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>vaX1LmWq</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>n1hhaOVo</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>OMDVg8x9</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr"/>
+      <c r="C297" t="inlineStr"/>
+      <c r="D297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>jXcAnQUr</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>fRe0c20b</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>fcYYQ80U</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>vm3yIDHa</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>KxZpVZPG</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>Ohp1YY1t</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>KKwAWCWh</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>l0VQSUVH</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>S2xgTDfT</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>bBbqoCon</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr"/>
+      <c r="C307" t="inlineStr"/>
+      <c r="D307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>8SfhEVGO</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>hYyIUj15</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>6y2iqjGb</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>nD6qGinC</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>4xLQ2Sg5</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>WOMI4lPh</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>4.75</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D255"/>
+  <dimension ref="A1:D314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4339,20 +4339,14 @@
           <t>tYjCfe2E</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="B245" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C245" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D245" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="246">
@@ -4361,20 +4355,14 @@
           <t>8UHsapgU</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="B246" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C246" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D246" t="n">
+        <v>2.45</v>
       </c>
     </row>
     <row r="247">
@@ -4383,20 +4371,14 @@
           <t>2meCcXHP</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="B247" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C247" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D247" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="248">
@@ -4405,20 +4387,14 @@
           <t>bJtrhBum</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
+      <c r="B248" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C248" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D248" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="249">
@@ -4427,20 +4403,14 @@
           <t>CrrhJmvn</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B249" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C249" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D249" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="250">
@@ -4449,20 +4419,14 @@
           <t>ILdqjkAa</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B250" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C250" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D250" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="251">
@@ -4471,20 +4435,14 @@
           <t>Qo0ilTvC</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="B251" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C251" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D251" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="252">
@@ -4493,20 +4451,14 @@
           <t>n1l0n79O</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
+      <c r="B252" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C252" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D252" t="n">
+        <v>2.63</v>
       </c>
     </row>
     <row r="253">
@@ -4515,20 +4467,14 @@
           <t>xQT96Aft</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="B253" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C253" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D253" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="254">
@@ -4537,20 +4483,14 @@
           <t>04EZ06OH</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="B254" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C254" t="n">
+        <v>4</v>
+      </c>
+      <c r="D254" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="255">
@@ -4559,19 +4499,963 @@
           <t>pCQRkLbJ</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>2.20</t>
+      <c r="B255" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C255" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D255" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>fmqtFMjD</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C256" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D256" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>8WpYGrM0</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C257" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D257" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>nHdPI4il</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C258" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D258" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>CntkHiGq</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="C259" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D259" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>hdlcFVpd</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C260" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D260" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>pjyqwZx3</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C261" t="n">
+        <v>5</v>
+      </c>
+      <c r="D261" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>tIUiyD7F</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C262" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D262" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>t4kJMDhM</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>8</v>
+      </c>
+      <c r="C263" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D263" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>Kl1AOZN9</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C264" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D264" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>697ha3El</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C265" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D265" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>634r8bcJ</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C266" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D266" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>pbFTwdnB</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="C267" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D267" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>vyoZBtbf</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C268" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D268" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>CnnJp4ae</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>2</v>
+      </c>
+      <c r="C269" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D269" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>bw1zAKS6</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C270" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D270" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>GINCsvmn</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C271" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D271" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>x6klsVh3</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C272" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D272" t="n">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>b3pRrrU7</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C273" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D273" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>WfkfPdXH</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>5</v>
+      </c>
+      <c r="C274" t="n">
+        <v>4</v>
+      </c>
+      <c r="D274" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>SMr3Nz2U</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C275" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D275" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>xYBLuIHb</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C276" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D276" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>6os5wmhS</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C277" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D277" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>Kl7vhn7L</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C278" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D278" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>nw6fJO5K</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C279" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D279" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>bHPacsq1</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C280" t="n">
+        <v>3</v>
+      </c>
+      <c r="D280" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>MwmHgKaN</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C281" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D281" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>lQl9etVA</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C282" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D282" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>KWD8eLDD</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C283" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D283" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>xUXzYQFk</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C284" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D284" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>CCV9JR0d</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C285" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D285" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>bsinRI25</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C286" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D286" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>GbaVU03t</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C287" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D287" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>tOTmlbNp</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C288" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D288" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>nPQL4PjR</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C289" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D289" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>pWhdu9NF</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C290" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D290" t="n">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>6NnRD2Ts</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C291" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D291" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>2FcwTvYh</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C292" t="n">
+        <v>5</v>
+      </c>
+      <c r="D292" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>EBSD6oME</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C293" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D293" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>WSQqW4p2</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C294" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D294" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>vaX1LmWq</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="C295" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D295" t="n">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>n1hhaOVo</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C296" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D296" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>OMDVg8x9</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>5</v>
+      </c>
+      <c r="C297" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D297" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>jXcAnQUr</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="C298" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D298" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>fRe0c20b</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C299" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D299" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>fcYYQ80U</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C300" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D300" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>vm3yIDHa</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C301" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D301" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>KxZpVZPG</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C302" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D302" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>Ohp1YY1t</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C303" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D303" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>KKwAWCWh</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C304" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D304" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>l0VQSUVH</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C305" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D305" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>S2xgTDfT</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C306" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D306" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>bBbqoCon</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C307" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D307" t="n">
+        <v>2.63</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>8SfhEVGO</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="C308" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D308" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>hYyIUj15</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C309" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D309" t="n">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>6y2iqjGb</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C310" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D310" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>nD6qGinC</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C311" t="n">
+        <v>4</v>
+      </c>
+      <c r="D311" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>4xLQ2Sg5</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C312" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D312" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>WOMI4lPh</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C313" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D313" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>AeRSxQrK</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>1.70</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D314"/>
+  <dimension ref="A1:D332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5443,19 +5443,409 @@
           <t>AeRSxQrK</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr">
+      <c r="B314" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C314" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D314" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>2g67Vsyf</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
         <is>
           <t>4.50</t>
         </is>
       </c>
-      <c r="C314" t="inlineStr">
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>U5cORazJ</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>dCkAk3SP</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>lAUlrLKa</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>fNaktakC</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2m3cvwKO</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>8j9FTL56</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>23e0sUpB</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>prkJckVi</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>6cwSeTa4</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>ENtzf7UG</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>6BI0ASEc</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>EyM886qA</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>YPYtjbTr</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
         <is>
           <t>4.20</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr">
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>zHg8u8FN</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>IycXZowo</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>fXlrhoaT</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
         <is>
           <t>1.70</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>j3zEnPMj</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>2.00</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D332"/>
+  <dimension ref="A1:D336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5459,20 +5459,14 @@
           <t>2g67Vsyf</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
+      <c r="B315" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C315" t="n">
+        <v>4</v>
+      </c>
+      <c r="D315" t="n">
+        <v>1.73</v>
       </c>
     </row>
     <row r="316">
@@ -5481,20 +5475,14 @@
           <t>U5cORazJ</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="B316" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C316" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D316" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="317">
@@ -5503,20 +5491,14 @@
           <t>dCkAk3SP</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
+      <c r="B317" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C317" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D317" t="n">
+        <v>4.1</v>
       </c>
     </row>
     <row r="318">
@@ -5525,20 +5507,14 @@
           <t>lAUlrLKa</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>23.00</t>
-        </is>
+      <c r="B318" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C318" t="n">
+        <v>10</v>
+      </c>
+      <c r="D318" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="319">
@@ -5547,20 +5523,14 @@
           <t>fNaktakC</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B319" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C319" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D319" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="320">
@@ -5569,20 +5539,14 @@
           <t>2m3cvwKO</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
+      <c r="B320" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C320" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D320" t="n">
+        <v>7.5</v>
       </c>
     </row>
     <row r="321">
@@ -5591,20 +5555,14 @@
           <t>8j9FTL56</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
+      <c r="B321" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C321" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D321" t="n">
+        <v>2.88</v>
       </c>
     </row>
     <row r="322">
@@ -5613,20 +5571,14 @@
           <t>23e0sUpB</t>
         </is>
       </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
+      <c r="B322" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C322" t="n">
+        <v>4</v>
+      </c>
+      <c r="D322" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="323">
@@ -5635,20 +5587,14 @@
           <t>prkJckVi</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
+      <c r="B323" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="C323" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D323" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="324">
@@ -5657,20 +5603,14 @@
           <t>6cwSeTa4</t>
         </is>
       </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="B324" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C324" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D324" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="325">
@@ -5679,20 +5619,14 @@
           <t>ENtzf7UG</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
+      <c r="B325" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C325" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D325" t="n">
+        <v>2.38</v>
       </c>
     </row>
     <row r="326">
@@ -5701,20 +5635,14 @@
           <t>6BI0ASEc</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="B326" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C326" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D326" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="327">
@@ -5723,20 +5651,14 @@
           <t>EyM886qA</t>
         </is>
       </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="B327" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C327" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D327" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="328">
@@ -5745,20 +5667,14 @@
           <t>YPYtjbTr</t>
         </is>
       </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="B328" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C328" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D328" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="329">
@@ -5767,20 +5683,14 @@
           <t>zHg8u8FN</t>
         </is>
       </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
+      <c r="B329" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C329" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D329" t="n">
+        <v>2.63</v>
       </c>
     </row>
     <row r="330">
@@ -5789,20 +5699,14 @@
           <t>IycXZowo</t>
         </is>
       </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B330" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C330" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D330" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="331">
@@ -5811,20 +5715,14 @@
           <t>fXlrhoaT</t>
         </is>
       </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="B331" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C331" t="n">
+        <v>4</v>
+      </c>
+      <c r="D331" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="332">
@@ -5833,19 +5731,101 @@
           <t>j3zEnPMj</t>
         </is>
       </c>
-      <c r="B332" t="inlineStr">
+      <c r="B332" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C332" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D332" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>GdWtpsjm</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>6RCbX36s</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>61T7bt5t</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>pKIPNiIj</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
         <is>
           <t>3.90</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>2.00</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D336"/>
+  <dimension ref="A1:D363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5747,20 +5747,14 @@
           <t>GdWtpsjm</t>
         </is>
       </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>13.00</t>
-        </is>
+      <c r="B333" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C333" t="n">
+        <v>7</v>
+      </c>
+      <c r="D333" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="334">
@@ -5769,20 +5763,14 @@
           <t>6RCbX36s</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="B334" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C334" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D334" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="335">
@@ -5791,20 +5779,14 @@
           <t>61T7bt5t</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
+      <c r="B335" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="C335" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D335" t="n">
+        <v>1.9</v>
       </c>
     </row>
     <row r="336">
@@ -5813,17 +5795,605 @@
           <t>pKIPNiIj</t>
         </is>
       </c>
-      <c r="B336" t="inlineStr">
+      <c r="B336" t="n">
+        <v>2</v>
+      </c>
+      <c r="C336" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D336" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>vDEpovX1</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
         <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="C336" t="inlineStr">
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>hxlYyYo4</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>U32wGjPp</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>hGzqjO6E</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>OrHrRGXo</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>WQF2UUMt</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>rkazN4LU</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
         <is>
           <t>3.40</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr">
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>GEugARyP</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>Wn71woN8</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>EkqxE9x0</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>dUjtW2Fr</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>MFnpCm7C</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>UsklUtpe</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>ddFjPf2b</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>Sh9BS8ig</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>dAfPwfHi</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>pWQ6LC1N</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>jiUEFsV1</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>dY0SOQjI</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>hO8aNYWA</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>vDA9yPiL</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>hzeTFV7m</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>Q9rcSKE7</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>zJCJQnM5</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>QkntzCGG</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>rRQ6H30k</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>YqcO2yDl</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
         <is>
           <t>3.90</t>
         </is>

--- a/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D363"/>
+  <dimension ref="A1:D490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5811,20 +5811,14 @@
           <t>vDEpovX1</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="B337" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C337" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D337" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="338">
@@ -5833,20 +5827,14 @@
           <t>hxlYyYo4</t>
         </is>
       </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
+      <c r="B338" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C338" t="n">
+        <v>4</v>
+      </c>
+      <c r="D338" t="n">
+        <v>1.67</v>
       </c>
     </row>
     <row r="339">
@@ -5855,20 +5843,14 @@
           <t>U32wGjPp</t>
         </is>
       </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
+      <c r="B339" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C339" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D339" t="n">
+        <v>1.42</v>
       </c>
     </row>
     <row r="340">
@@ -5877,20 +5859,14 @@
           <t>hGzqjO6E</t>
         </is>
       </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
+      <c r="B340" t="n">
+        <v>5</v>
+      </c>
+      <c r="C340" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D340" t="n">
+        <v>1.62</v>
       </c>
     </row>
     <row r="341">
@@ -5899,20 +5875,14 @@
           <t>OrHrRGXo</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>12.00</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
+      <c r="B341" t="n">
+        <v>12</v>
+      </c>
+      <c r="C341" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="D341" t="n">
+        <v>1.22</v>
       </c>
     </row>
     <row r="342">
@@ -5921,20 +5891,14 @@
           <t>WQF2UUMt</t>
         </is>
       </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B342" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C342" t="n">
+        <v>4</v>
+      </c>
+      <c r="D342" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="343">
@@ -5943,20 +5907,14 @@
           <t>rkazN4LU</t>
         </is>
       </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B343" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C343" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D343" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="344">
@@ -5965,20 +5923,14 @@
           <t>GEugARyP</t>
         </is>
       </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B344" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C344" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D344" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="345">
@@ -5987,20 +5939,14 @@
           <t>Wn71woN8</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
+      <c r="B345" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C345" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D345" t="n">
+        <v>1.85</v>
       </c>
     </row>
     <row r="346">
@@ -6009,20 +5955,14 @@
           <t>EkqxE9x0</t>
         </is>
       </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>13.00</t>
-        </is>
+      <c r="B346" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="C346" t="n">
+        <v>7</v>
+      </c>
+      <c r="D346" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="347">
@@ -6031,20 +5971,14 @@
           <t>dUjtW2Fr</t>
         </is>
       </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="B347" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C347" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D347" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="348">
@@ -6053,20 +5987,14 @@
           <t>MFnpCm7C</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
+      <c r="B348" t="n">
+        <v>4</v>
+      </c>
+      <c r="C348" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D348" t="n">
+        <v>1.9</v>
       </c>
     </row>
     <row r="349">
@@ -6075,20 +6003,14 @@
           <t>UsklUtpe</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="B349" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C349" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D349" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="350">
@@ -6097,20 +6019,14 @@
           <t>ddFjPf2b</t>
         </is>
       </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>12.00</t>
-        </is>
+      <c r="B350" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="C350" t="n">
+        <v>8</v>
+      </c>
+      <c r="D350" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="351">
@@ -6119,20 +6035,14 @@
           <t>Sh9BS8ig</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
+      <c r="B351" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C351" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D351" t="n">
+        <v>5.75</v>
       </c>
     </row>
     <row r="352">
@@ -6141,20 +6051,14 @@
           <t>dAfPwfHi</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>13.00</t>
-        </is>
+      <c r="B352" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="C352" t="n">
+        <v>8</v>
+      </c>
+      <c r="D352" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="353">
@@ -6163,20 +6067,14 @@
           <t>pWQ6LC1N</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="B353" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C353" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D353" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="354">
@@ -6185,20 +6083,14 @@
           <t>jiUEFsV1</t>
         </is>
       </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
+      <c r="B354" t="n">
+        <v>5</v>
+      </c>
+      <c r="C354" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D354" t="n">
+        <v>1.7</v>
       </c>
     </row>
     <row r="355">
@@ -6207,20 +6099,14 @@
           <t>dY0SOQjI</t>
         </is>
       </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
+      <c r="B355" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="C355" t="n">
+        <v>4</v>
+      </c>
+      <c r="D355" t="n">
+        <v>1.57</v>
       </c>
     </row>
     <row r="356">
@@ -6229,20 +6115,14 @@
           <t>hO8aNYWA</t>
         </is>
       </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>13.00</t>
-        </is>
+      <c r="B356" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="C356" t="n">
+        <v>9</v>
+      </c>
+      <c r="D356" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="357">
@@ -6251,20 +6131,14 @@
           <t>vDA9yPiL</t>
         </is>
       </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B357" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C357" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D357" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="358">
@@ -6273,20 +6147,14 @@
           <t>hzeTFV7m</t>
         </is>
       </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="B358" t="n">
+        <v>3</v>
+      </c>
+      <c r="C358" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D358" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="359">
@@ -6295,20 +6163,14 @@
           <t>Q9rcSKE7</t>
         </is>
       </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
+      <c r="B359" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C359" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D359" t="n">
+        <v>1.73</v>
       </c>
     </row>
     <row r="360">
@@ -6317,20 +6179,14 @@
           <t>zJCJQnM5</t>
         </is>
       </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D360" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
+      <c r="B360" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C360" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D360" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="361">
@@ -6339,20 +6195,14 @@
           <t>QkntzCGG</t>
         </is>
       </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
+      <c r="B361" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C361" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D361" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="362">
@@ -6361,20 +6211,14 @@
           <t>rRQ6H30k</t>
         </is>
       </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C362" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
+      <c r="B362" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C362" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D362" t="n">
+        <v>4.1</v>
       </c>
     </row>
     <row r="363">
@@ -6383,19 +6227,1607 @@
           <t>YqcO2yDl</t>
         </is>
       </c>
-      <c r="B363" t="inlineStr">
+      <c r="B363" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C363" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D363" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>INsZAAf3</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>8QPOfb45</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>x6HuiG3U</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t>SUdkBJln</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="inlineStr">
+        <is>
+          <t>lpob9cJb</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
         <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="C363" t="inlineStr">
+    </row>
+    <row r="369">
+      <c r="A369" s="1" t="inlineStr">
+        <is>
+          <t>2Fanm72d</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="inlineStr">
+        <is>
+          <t>ERWFdKZh</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t>hEytAlL6</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr"/>
+      <c r="C371" t="inlineStr"/>
+      <c r="D371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t>IkSxE8Dt</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr"/>
+      <c r="C372" t="inlineStr"/>
+      <c r="D372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>AqLzFcCb</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr"/>
+      <c r="C373" t="inlineStr"/>
+      <c r="D373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>6kw90bc5</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr"/>
+      <c r="C374" t="inlineStr"/>
+      <c r="D374" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>jyz8Ixzp</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr"/>
+      <c r="C375" t="inlineStr"/>
+      <c r="D375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>KW71BLSG</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr"/>
+      <c r="C376" t="inlineStr"/>
+      <c r="D376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>4zQgCGV0</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr"/>
+      <c r="C377" t="inlineStr"/>
+      <c r="D377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>plYXBAjf</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr"/>
+      <c r="C378" t="inlineStr"/>
+      <c r="D378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>K8al4YeU</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr"/>
+      <c r="C379" t="inlineStr"/>
+      <c r="D379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>d6nbgHsC</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr"/>
+      <c r="C380" t="inlineStr"/>
+      <c r="D380" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>E3bH2ZAd</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr"/>
+      <c r="C381" t="inlineStr"/>
+      <c r="D381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>hQRLDaJc</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr"/>
+      <c r="C382" t="inlineStr"/>
+      <c r="D382" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>OSEc76Ak</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr"/>
+      <c r="C383" t="inlineStr"/>
+      <c r="D383" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>rFdeX5Xp</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr"/>
+      <c r="C384" t="inlineStr"/>
+      <c r="D384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>GhQhDBYp</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr"/>
+      <c r="C385" t="inlineStr"/>
+      <c r="D385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>6BbKeRcC</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr"/>
+      <c r="C386" t="inlineStr"/>
+      <c r="D386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="inlineStr">
+        <is>
+          <t>v3yHbxSH</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr"/>
+      <c r="C387" t="inlineStr"/>
+      <c r="D387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="inlineStr">
+        <is>
+          <t>pvekOSfU</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="inlineStr">
+        <is>
+          <t>C4BrrfEE</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr"/>
+      <c r="C389" t="inlineStr"/>
+      <c r="D389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="inlineStr">
+        <is>
+          <t>IVsJZ1cE</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr"/>
+      <c r="C390" t="inlineStr"/>
+      <c r="D390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="inlineStr">
+        <is>
+          <t>Ot6u6fRH</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr"/>
+      <c r="C391" t="inlineStr"/>
+      <c r="D391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="inlineStr">
+        <is>
+          <t>ANq02KSh</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr"/>
+      <c r="C392" t="inlineStr"/>
+      <c r="D392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="inlineStr">
+        <is>
+          <t>Gb1A9acT</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr"/>
+      <c r="C393" t="inlineStr"/>
+      <c r="D393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>C43kVFJk</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr"/>
+      <c r="C394" t="inlineStr"/>
+      <c r="D394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="inlineStr">
+        <is>
+          <t>jXaKcHG7</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr"/>
+      <c r="C395" t="inlineStr"/>
+      <c r="D395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="inlineStr">
+        <is>
+          <t>KhqxObCM</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr"/>
+      <c r="C396" t="inlineStr"/>
+      <c r="D396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="inlineStr">
+        <is>
+          <t>K6OAxbRF</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr"/>
+      <c r="C397" t="inlineStr"/>
+      <c r="D397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="inlineStr">
+        <is>
+          <t>vcIeQx33</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr"/>
+      <c r="C398" t="inlineStr"/>
+      <c r="D398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="inlineStr">
+        <is>
+          <t>4Cs7LK8E</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="inlineStr">
+        <is>
+          <t>W61W8sP8</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr"/>
+      <c r="C400" t="inlineStr"/>
+      <c r="D400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="1" t="inlineStr">
+        <is>
+          <t>bJWjBFBN</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr"/>
+      <c r="C401" t="inlineStr"/>
+      <c r="D401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="inlineStr">
+        <is>
+          <t>j9HX6LgL</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr"/>
+      <c r="C402" t="inlineStr"/>
+      <c r="D402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="inlineStr">
+        <is>
+          <t>M5JxAHIM</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="inlineStr">
+        <is>
+          <t>C64gDsb4</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr"/>
+      <c r="C404" t="inlineStr"/>
+      <c r="D404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="inlineStr">
+        <is>
+          <t>xEisQlQH</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr"/>
+      <c r="C405" t="inlineStr"/>
+      <c r="D405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="inlineStr">
+        <is>
+          <t>4Wk6ieCO</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr"/>
+      <c r="C406" t="inlineStr"/>
+      <c r="D406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="inlineStr">
+        <is>
+          <t>WprGGG4d</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr"/>
+      <c r="C407" t="inlineStr"/>
+      <c r="D407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>tzIzWVsQ</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>vwhQPEQG</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr"/>
+      <c r="C409" t="inlineStr"/>
+      <c r="D409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>vuaksbnB</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr"/>
+      <c r="C410" t="inlineStr"/>
+      <c r="D410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>0YJgAQC5</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr"/>
+      <c r="C411" t="inlineStr"/>
+      <c r="D411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>pbJdKjM7</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr"/>
+      <c r="C412" t="inlineStr"/>
+      <c r="D412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>SQfscarm</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr"/>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>jqtRXuSQ</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr"/>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>jT7X7Gd5</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr"/>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>dIO7tAAb</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr"/>
+      <c r="C416" t="inlineStr"/>
+      <c r="D416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>WKO7Omz0</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>tj094etp</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr"/>
+      <c r="C418" t="inlineStr"/>
+      <c r="D418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>tr0QWSff</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr"/>
+      <c r="C419" t="inlineStr"/>
+      <c r="D419" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>I9OrDysB</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr"/>
+      <c r="C420" t="inlineStr"/>
+      <c r="D420" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>jDiLRtDc</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr"/>
+      <c r="C421" t="inlineStr"/>
+      <c r="D421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>6Xq5xjLq</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr"/>
+      <c r="C422" t="inlineStr"/>
+      <c r="D422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>ALlse9Pi</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr"/>
+      <c r="C423" t="inlineStr"/>
+      <c r="D423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>CpJVj93N</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>Mi831aHr</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr"/>
+      <c r="C425" t="inlineStr"/>
+      <c r="D425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>SnzzjdRj</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr"/>
+      <c r="C426" t="inlineStr"/>
+      <c r="D426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>8G41omRp</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr"/>
+      <c r="C427" t="inlineStr"/>
+      <c r="D427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>jHHGvluB</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr"/>
+      <c r="C428" t="inlineStr"/>
+      <c r="D428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>OvV1vKd3</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr"/>
+      <c r="C429" t="inlineStr"/>
+      <c r="D429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>f1EO9xSh</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr"/>
+      <c r="C430" t="inlineStr"/>
+      <c r="D430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>IBytSAe5</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr"/>
+      <c r="C431" t="inlineStr"/>
+      <c r="D431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>bweTPKsA</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr"/>
+      <c r="C432" t="inlineStr"/>
+      <c r="D432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>lUWRGJsn</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr"/>
+      <c r="C433" t="inlineStr"/>
+      <c r="D433" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>GIPMhVYA</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr"/>
+      <c r="C434" t="inlineStr"/>
+      <c r="D434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>ATMcSJkl</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr"/>
+      <c r="C435" t="inlineStr"/>
+      <c r="D435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>OUFOxS9N</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>roLym02k</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr"/>
+      <c r="C437" t="inlineStr"/>
+      <c r="D437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>pbwYTWQh</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr"/>
+      <c r="C438" t="inlineStr"/>
+      <c r="D438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>Wzwjgmf4</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr"/>
+      <c r="C439" t="inlineStr"/>
+      <c r="D439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>GW4e7Um4</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr"/>
+      <c r="C440" t="inlineStr"/>
+      <c r="D440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>EuGUBwlA</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr"/>
+      <c r="C441" t="inlineStr"/>
+      <c r="D441" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>8pGGBbct</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr"/>
+      <c r="C442" t="inlineStr"/>
+      <c r="D442" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2yu5QcK0</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr"/>
+      <c r="C443" t="inlineStr"/>
+      <c r="D443" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>ltVl8SkJ</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr"/>
+      <c r="C444" t="inlineStr"/>
+      <c r="D444" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>OrVmMCie</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr"/>
+      <c r="C445" t="inlineStr"/>
+      <c r="D445" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>b5iIdGdU</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr"/>
+      <c r="C446" t="inlineStr"/>
+      <c r="D446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>Ac09TdRi</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr"/>
+      <c r="C447" t="inlineStr"/>
+      <c r="D447" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>Ey2Sg5SO</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr"/>
+      <c r="C448" t="inlineStr"/>
+      <c r="D448" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>ETqpict9</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr"/>
+      <c r="C449" t="inlineStr"/>
+      <c r="D449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="inlineStr">
+        <is>
+          <t>GUs6MFBb</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr"/>
+      <c r="C450" t="inlineStr"/>
+      <c r="D450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="inlineStr">
+        <is>
+          <t>dAMoEx1l</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr"/>
+      <c r="C451" t="inlineStr"/>
+      <c r="D451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>xng458IG</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr"/>
+      <c r="C452" t="inlineStr"/>
+      <c r="D452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>0fDYRkv8</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr"/>
+      <c r="C453" t="inlineStr"/>
+      <c r="D453" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>CUnt4wLj</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr"/>
+      <c r="C454" t="inlineStr"/>
+      <c r="D454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>fkIM5gZp</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>r7dCawne</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr"/>
+      <c r="C456" t="inlineStr"/>
+      <c r="D456" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>xQuFJbwR</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr"/>
+      <c r="C457" t="inlineStr"/>
+      <c r="D457" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>46QpCnrg</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr"/>
+      <c r="C458" t="inlineStr"/>
+      <c r="D458" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>OjTDOykD</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr"/>
+      <c r="C459" t="inlineStr"/>
+      <c r="D459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>OOnl9jJi</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr"/>
+      <c r="C460" t="inlineStr"/>
+      <c r="D460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="inlineStr">
+        <is>
+          <t>YoI184sI</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr"/>
+      <c r="C461" t="inlineStr"/>
+      <c r="D461" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="inlineStr">
+        <is>
+          <t>EwFQTB9e</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr"/>
+      <c r="C462" t="inlineStr"/>
+      <c r="D462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>zgw9F7bE</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="inlineStr">
+        <is>
+          <t>hzDGMR4C</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr"/>
+      <c r="C464" t="inlineStr"/>
+      <c r="D464" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="inlineStr">
+        <is>
+          <t>0vgkewDa</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr"/>
+      <c r="C465" t="inlineStr"/>
+      <c r="D465" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="inlineStr">
+        <is>
+          <t>KMvNIXAN</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr"/>
+      <c r="C466" t="inlineStr"/>
+      <c r="D466" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="inlineStr">
+        <is>
+          <t>pG6HYlQs</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr"/>
+      <c r="C467" t="inlineStr"/>
+      <c r="D467" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="inlineStr">
+        <is>
+          <t>lhLarWun</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="inlineStr">
+        <is>
+          <t>OfoEKgtB</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr"/>
+      <c r="C469" t="inlineStr"/>
+      <c r="D469" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="inlineStr">
+        <is>
+          <t>bZvl4Jlo</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr"/>
+      <c r="C470" t="inlineStr"/>
+      <c r="D470" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>lWqPVhdt</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr"/>
+      <c r="C471" t="inlineStr"/>
+      <c r="D471" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>OfLaQ95m</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr"/>
+      <c r="C472" t="inlineStr"/>
+      <c r="D472" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>fFgcOysn</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr"/>
+      <c r="C473" t="inlineStr"/>
+      <c r="D473" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>QkE2Af0D</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr"/>
+      <c r="C474" t="inlineStr"/>
+      <c r="D474" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="inlineStr">
+        <is>
+          <t>2cth4tbt</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr"/>
+      <c r="C475" t="inlineStr"/>
+      <c r="D475" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="inlineStr">
+        <is>
+          <t>Ma8YsCcM</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr"/>
+      <c r="C476" t="inlineStr"/>
+      <c r="D476" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="inlineStr">
+        <is>
+          <t>bL1cTgl2</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr"/>
+      <c r="C477" t="inlineStr"/>
+      <c r="D477" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="inlineStr">
+        <is>
+          <t>IN3HRzd4</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr"/>
+      <c r="C478" t="inlineStr"/>
+      <c r="D478" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="inlineStr">
+        <is>
+          <t>OYqPDWLs</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr"/>
+      <c r="C479" t="inlineStr"/>
+      <c r="D479" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="inlineStr">
+        <is>
+          <t>fJggJhbK</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr"/>
+      <c r="C480" t="inlineStr"/>
+      <c r="D480" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="inlineStr">
+        <is>
+          <t>82DqAJKE</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="1" t="inlineStr">
+        <is>
+          <t>4U6h8ckR</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="inlineStr">
+        <is>
+          <t>faoX0Fs1</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="inlineStr">
+        <is>
+          <t>2PluagCD</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="inlineStr">
+        <is>
+          <t>IXWRMd4K</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="inlineStr">
+        <is>
+          <t>E3IcHzSs</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="inlineStr">
+        <is>
+          <t>YuaKqZvA</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr">
+        <is>
+          <t>KtXllxbe</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>xE5BoeAc</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
         <is>
           <t>3.50</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>3.90</t>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>G8QcnGS7</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>3.70</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D490"/>
+  <dimension ref="A1:D495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6243,20 +6243,14 @@
           <t>INsZAAf3</t>
         </is>
       </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-      <c r="C364" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D364" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
+      <c r="B364" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C364" t="n">
+        <v>5</v>
+      </c>
+      <c r="D364" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="365">
@@ -6265,20 +6259,14 @@
           <t>8QPOfb45</t>
         </is>
       </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C365" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B365" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C365" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D365" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="366">
@@ -6287,20 +6275,14 @@
           <t>x6HuiG3U</t>
         </is>
       </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C366" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D366" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="B366" t="n">
+        <v>3</v>
+      </c>
+      <c r="C366" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D366" t="n">
+        <v>2.35</v>
       </c>
     </row>
     <row r="367">
@@ -6309,20 +6291,14 @@
           <t>SUdkBJln</t>
         </is>
       </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
+      <c r="B367" t="n">
+        <v>3</v>
+      </c>
+      <c r="C367" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D367" t="n">
+        <v>2.38</v>
       </c>
     </row>
     <row r="368">
@@ -6331,20 +6307,14 @@
           <t>lpob9cJb</t>
         </is>
       </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="C368" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D368" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
+      <c r="B368" t="n">
+        <v>4</v>
+      </c>
+      <c r="C368" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D368" t="n">
+        <v>1.85</v>
       </c>
     </row>
     <row r="369">
@@ -6353,20 +6323,14 @@
           <t>2Fanm72d</t>
         </is>
       </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C369" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="B369" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C369" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D369" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="370">
@@ -6375,20 +6339,14 @@
           <t>ERWFdKZh</t>
         </is>
       </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
+      <c r="B370" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C370" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D370" t="n">
+        <v>7.5</v>
       </c>
     </row>
     <row r="371">
@@ -6567,20 +6525,14 @@
           <t>pvekOSfU</t>
         </is>
       </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="C388" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B388" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C388" t="n">
+        <v>5</v>
+      </c>
+      <c r="D388" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="389">
@@ -6689,20 +6641,14 @@
           <t>4Cs7LK8E</t>
         </is>
       </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C399" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B399" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C399" t="n">
+        <v>4</v>
+      </c>
+      <c r="D399" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="400">
@@ -6741,20 +6687,14 @@
           <t>M5JxAHIM</t>
         </is>
       </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
+      <c r="B403" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C403" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D403" t="n">
+        <v>1.55</v>
       </c>
     </row>
     <row r="404">
@@ -6803,20 +6743,14 @@
           <t>tzIzWVsQ</t>
         </is>
       </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="B408" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C408" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D408" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="409">
@@ -6905,20 +6839,14 @@
           <t>WKO7Omz0</t>
         </is>
       </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="B417" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C417" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D417" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="418">
@@ -6987,20 +6915,14 @@
           <t>CpJVj93N</t>
         </is>
       </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B424" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="C424" t="n">
+        <v>5</v>
+      </c>
+      <c r="D424" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="425">
@@ -7119,20 +7041,14 @@
           <t>OUFOxS9N</t>
         </is>
       </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C436" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="B436" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C436" t="n">
+        <v>4</v>
+      </c>
+      <c r="D436" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="437">
@@ -7321,20 +7237,14 @@
           <t>fkIM5gZp</t>
         </is>
       </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C455" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="B455" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C455" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D455" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="456">
@@ -7413,20 +7323,14 @@
           <t>zgw9F7bE</t>
         </is>
       </c>
-      <c r="B463" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="C463" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D463" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
+      <c r="B463" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C463" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D463" t="n">
+        <v>2.05</v>
       </c>
     </row>
     <row r="464">
@@ -7475,20 +7379,14 @@
           <t>lhLarWun</t>
         </is>
       </c>
-      <c r="B468" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="C468" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D468" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
+      <c r="B468" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C468" t="n">
+        <v>5</v>
+      </c>
+      <c r="D468" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="469">
@@ -7617,20 +7515,14 @@
           <t>82DqAJKE</t>
         </is>
       </c>
-      <c r="B481" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C481" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="B481" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C481" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D481" t="n">
+        <v>2.55</v>
       </c>
     </row>
     <row r="482">
@@ -7639,20 +7531,14 @@
           <t>4U6h8ckR</t>
         </is>
       </c>
-      <c r="B482" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D482" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
+      <c r="B482" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="C482" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D482" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="483">
@@ -7661,20 +7547,14 @@
           <t>faoX0Fs1</t>
         </is>
       </c>
-      <c r="B483" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C483" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D483" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B483" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C483" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D483" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="484">
@@ -7683,20 +7563,14 @@
           <t>2PluagCD</t>
         </is>
       </c>
-      <c r="B484" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="C484" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D484" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
+      <c r="B484" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C484" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D484" t="n">
+        <v>2.63</v>
       </c>
     </row>
     <row r="485">
@@ -7705,20 +7579,14 @@
           <t>IXWRMd4K</t>
         </is>
       </c>
-      <c r="B485" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D485" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="B485" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C485" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D485" t="n">
+        <v>2.1</v>
       </c>
     </row>
     <row r="486">
@@ -7727,20 +7595,14 @@
           <t>E3IcHzSs</t>
         </is>
       </c>
-      <c r="B486" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D486" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
+      <c r="B486" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C486" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D486" t="n">
+        <v>1.91</v>
       </c>
     </row>
     <row r="487">
@@ -7749,20 +7611,14 @@
           <t>YuaKqZvA</t>
         </is>
       </c>
-      <c r="B487" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D487" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="B487" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C487" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D487" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="488">
@@ -7771,20 +7627,14 @@
           <t>KtXllxbe</t>
         </is>
       </c>
-      <c r="B488" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C488" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D488" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="B488" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C488" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D488" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="489">
@@ -7793,20 +7643,14 @@
           <t>xE5BoeAc</t>
         </is>
       </c>
-      <c r="B489" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D489" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="B489" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C489" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D489" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="490">
@@ -7815,19 +7659,111 @@
           <t>G8QcnGS7</t>
         </is>
       </c>
-      <c r="B490" t="inlineStr">
+      <c r="B490" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C490" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D490" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>z1q67ylB</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
         <is>
           <t>1.91</t>
         </is>
       </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>3.70</t>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>tvOWhxZH</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>U11vkTXq</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>SWRIzxdS</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr"/>
+      <c r="C494" t="inlineStr"/>
+      <c r="D494" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>KGmbFEdf</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>3.90</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D619"/>
+  <dimension ref="A1:D627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8077,20 +8077,14 @@
           <t>Wplk7SgS</t>
         </is>
       </c>
-      <c r="B524" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C524" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D524" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B524" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C524" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D524" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="525">
@@ -8099,20 +8093,14 @@
           <t>2TvL16Hk</t>
         </is>
       </c>
-      <c r="B525" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="C525" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D525" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
+      <c r="B525" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C525" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D525" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="526">
@@ -8121,20 +8109,14 @@
           <t>beYTapn2</t>
         </is>
       </c>
-      <c r="B526" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C526" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D526" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B526" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C526" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D526" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="527">
@@ -8143,20 +8125,14 @@
           <t>jkLFNmv9</t>
         </is>
       </c>
-      <c r="B527" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C527" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D527" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B527" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C527" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D527" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="528">
@@ -8165,20 +8141,14 @@
           <t>AiyHLR8L</t>
         </is>
       </c>
-      <c r="B528" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="C528" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-      <c r="D528" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
+      <c r="B528" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C528" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="D528" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="529">
@@ -8187,20 +8157,14 @@
           <t>tzSnG5Wr</t>
         </is>
       </c>
-      <c r="B529" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="C529" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-      <c r="D529" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
+      <c r="B529" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="C529" t="n">
+        <v>8</v>
+      </c>
+      <c r="D529" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="530">
@@ -8209,20 +8173,14 @@
           <t>2kGeEq1e</t>
         </is>
       </c>
-      <c r="B530" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="C530" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D530" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
+      <c r="B530" t="n">
+        <v>4</v>
+      </c>
+      <c r="C530" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D530" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="531">
@@ -8251,20 +8209,14 @@
           <t>OhdEZ36b</t>
         </is>
       </c>
-      <c r="B533" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C533" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D533" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="B533" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C533" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D533" t="n">
+        <v>3.9</v>
       </c>
     </row>
     <row r="534">
@@ -8273,20 +8225,14 @@
           <t>I9KbIKLH</t>
         </is>
       </c>
-      <c r="B534" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C534" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D534" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="B534" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C534" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D534" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="535">
@@ -8315,20 +8261,14 @@
           <t>K4VeyRD5</t>
         </is>
       </c>
-      <c r="B537" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C537" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D537" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
+      <c r="B537" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C537" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D537" t="n">
+        <v>2.63</v>
       </c>
     </row>
     <row r="538">
@@ -8367,20 +8307,14 @@
           <t>jaUqrSMj</t>
         </is>
       </c>
-      <c r="B541" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="C541" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D541" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="B541" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C541" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D541" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="542">
@@ -8409,20 +8343,14 @@
           <t>WW4IdRyp</t>
         </is>
       </c>
-      <c r="B544" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="C544" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D544" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B544" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C544" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D544" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="545">
@@ -8431,20 +8359,14 @@
           <t>pIFVy6I7</t>
         </is>
       </c>
-      <c r="B545" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="C545" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D545" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
+      <c r="B545" t="n">
+        <v>4</v>
+      </c>
+      <c r="C545" t="n">
+        <v>4</v>
+      </c>
+      <c r="D545" t="n">
+        <v>1.62</v>
       </c>
     </row>
     <row r="546">
@@ -8453,20 +8375,14 @@
           <t>IsdlPSY1</t>
         </is>
       </c>
-      <c r="B546" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C546" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D546" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="B546" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C546" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D546" t="n">
+        <v>2.4</v>
       </c>
     </row>
     <row r="547">
@@ -8485,20 +8401,14 @@
           <t>WWGbDMV6</t>
         </is>
       </c>
-      <c r="B548" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="C548" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="D548" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
+      <c r="B548" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C548" t="n">
+        <v>6</v>
+      </c>
+      <c r="D548" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="549">
@@ -8527,20 +8437,14 @@
           <t>Sxox9eR6</t>
         </is>
       </c>
-      <c r="B551" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="C551" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D551" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
+      <c r="B551" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C551" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D551" t="n">
+        <v>1.91</v>
       </c>
     </row>
     <row r="552">
@@ -8549,20 +8453,14 @@
           <t>fTrEmlaT</t>
         </is>
       </c>
-      <c r="B552" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C552" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D552" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="B552" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C552" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D552" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="553">
@@ -8581,20 +8479,14 @@
           <t>6kJ094Lk</t>
         </is>
       </c>
-      <c r="B554" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="C554" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D554" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
+      <c r="B554" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C554" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D554" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="555">
@@ -8613,20 +8505,14 @@
           <t>lUSsM2Mh</t>
         </is>
       </c>
-      <c r="B556" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C556" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D556" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="B556" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C556" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D556" t="n">
+        <v>2.4</v>
       </c>
     </row>
     <row r="557">
@@ -8645,20 +8531,14 @@
           <t>zalWK5TO</t>
         </is>
       </c>
-      <c r="B558" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C558" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D558" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B558" t="n">
+        <v>2</v>
+      </c>
+      <c r="C558" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D558" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="559">
@@ -8667,20 +8547,14 @@
           <t>YRgnVhvd</t>
         </is>
       </c>
-      <c r="B559" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C559" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D559" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="B559" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C559" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D559" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="560">
@@ -8699,20 +8573,14 @@
           <t>zRfR2QoD</t>
         </is>
       </c>
-      <c r="B561" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="C561" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="D561" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="B561" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C561" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D561" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="562">
@@ -8721,20 +8589,14 @@
           <t>UN4eVor9</t>
         </is>
       </c>
-      <c r="B562" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="C562" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D562" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="B562" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C562" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D562" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="563">
@@ -8743,20 +8605,14 @@
           <t>pdMjKti5</t>
         </is>
       </c>
-      <c r="B563" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="C563" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D563" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B563" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C563" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D563" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="564">
@@ -8775,20 +8631,14 @@
           <t>2DUZNOit</t>
         </is>
       </c>
-      <c r="B565" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="C565" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D565" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B565" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C565" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D565" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="566">
@@ -8797,20 +8647,14 @@
           <t>KQM2PGBm</t>
         </is>
       </c>
-      <c r="B566" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="C566" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D566" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="B566" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C566" t="n">
+        <v>4</v>
+      </c>
+      <c r="D566" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="567">
@@ -8819,20 +8663,14 @@
           <t>SvvsVc5N</t>
         </is>
       </c>
-      <c r="B567" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C567" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D567" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B567" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C567" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D567" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="568">
@@ -8841,20 +8679,14 @@
           <t>0QcIa9AE</t>
         </is>
       </c>
-      <c r="B568" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="C568" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D568" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
+      <c r="B568" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C568" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D568" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="569">
@@ -8863,20 +8695,14 @@
           <t>SbbRf56d</t>
         </is>
       </c>
-      <c r="B569" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="C569" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D569" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
+      <c r="B569" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C569" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D569" t="n">
+        <v>7.5</v>
       </c>
     </row>
     <row r="570">
@@ -8885,20 +8711,14 @@
           <t>pWf4j5X0</t>
         </is>
       </c>
-      <c r="B570" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="C570" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D570" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
+      <c r="B570" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C570" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D570" t="n">
+        <v>6.25</v>
       </c>
     </row>
     <row r="571">
@@ -8917,20 +8737,14 @@
           <t>EXFv49qA</t>
         </is>
       </c>
-      <c r="B572" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C572" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D572" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="B572" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C572" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D572" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="573">
@@ -8939,20 +8753,14 @@
           <t>b1HNwSme</t>
         </is>
       </c>
-      <c r="B573" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C573" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D573" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
+      <c r="B573" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C573" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D573" t="n">
+        <v>3.75</v>
       </c>
     </row>
     <row r="574">
@@ -8981,20 +8789,14 @@
           <t>6mIDMoQH</t>
         </is>
       </c>
-      <c r="B576" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="C576" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D576" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
+      <c r="B576" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="C576" t="n">
+        <v>4</v>
+      </c>
+      <c r="D576" t="n">
+        <v>1.42</v>
       </c>
     </row>
     <row r="577">
@@ -9003,20 +8805,14 @@
           <t>l6EJLYAC</t>
         </is>
       </c>
-      <c r="B577" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="C577" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="D577" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
+      <c r="B577" t="n">
+        <v>7</v>
+      </c>
+      <c r="C577" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D577" t="n">
+        <v>1.27</v>
       </c>
     </row>
     <row r="578">
@@ -9025,20 +8821,14 @@
           <t>zm4m2mEM</t>
         </is>
       </c>
-      <c r="B578" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C578" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D578" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="B578" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C578" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D578" t="n">
+        <v>2.45</v>
       </c>
     </row>
     <row r="579">
@@ -9047,20 +8837,14 @@
           <t>EFM87rj2</t>
         </is>
       </c>
-      <c r="B579" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
-      </c>
-      <c r="C579" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="D579" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
+      <c r="B579" t="n">
+        <v>10</v>
+      </c>
+      <c r="C579" t="n">
+        <v>6</v>
+      </c>
+      <c r="D579" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="580">
@@ -9089,20 +8873,14 @@
           <t>OnsQYu6b</t>
         </is>
       </c>
-      <c r="B582" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="C582" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="D582" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
+      <c r="B582" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C582" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D582" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="583">
@@ -9111,20 +8889,14 @@
           <t>EyE7GbjU</t>
         </is>
       </c>
-      <c r="B583" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C583" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D583" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B583" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C583" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D583" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="584">
@@ -9133,20 +8905,14 @@
           <t>Y7eVkQSb</t>
         </is>
       </c>
-      <c r="B584" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C584" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D584" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="B584" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C584" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D584" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="585">
@@ -9175,20 +8941,14 @@
           <t>h4nciWa4</t>
         </is>
       </c>
-      <c r="B587" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="C587" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D587" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B587" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C587" t="n">
+        <v>4</v>
+      </c>
+      <c r="D587" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="588">
@@ -9207,20 +8967,14 @@
           <t>Iqy8qcKG</t>
         </is>
       </c>
-      <c r="B589" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="C589" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D589" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
+      <c r="B589" t="n">
+        <v>4</v>
+      </c>
+      <c r="C589" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D589" t="n">
+        <v>1.75</v>
       </c>
     </row>
     <row r="590">
@@ -9229,20 +8983,14 @@
           <t>GWO4Z4rI</t>
         </is>
       </c>
-      <c r="B590" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C590" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D590" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B590" t="n">
+        <v>2</v>
+      </c>
+      <c r="C590" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D590" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="591">
@@ -9251,20 +8999,14 @@
           <t>2gzn8nBO</t>
         </is>
       </c>
-      <c r="B591" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="C591" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D591" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
+      <c r="B591" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C591" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D591" t="n">
+        <v>1.57</v>
       </c>
     </row>
     <row r="592">
@@ -9273,20 +9015,14 @@
           <t>MN2wyBFN</t>
         </is>
       </c>
-      <c r="B592" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="C592" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D592" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B592" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C592" t="n">
+        <v>4</v>
+      </c>
+      <c r="D592" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="593">
@@ -9305,20 +9041,14 @@
           <t>4r62Vlwo</t>
         </is>
       </c>
-      <c r="B594" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C594" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D594" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="B594" t="n">
+        <v>3</v>
+      </c>
+      <c r="C594" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D594" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="595">
@@ -9347,20 +9077,14 @@
           <t>hvLANft0</t>
         </is>
       </c>
-      <c r="B597" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="C597" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D597" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="B597" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C597" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D597" t="n">
+        <v>2.2</v>
       </c>
     </row>
     <row r="598">
@@ -9369,20 +9093,14 @@
           <t>0E33lZ3q</t>
         </is>
       </c>
-      <c r="B598" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="C598" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D598" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
+      <c r="B598" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C598" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D598" t="n">
+        <v>1.85</v>
       </c>
     </row>
     <row r="599">
@@ -9391,20 +9109,14 @@
           <t>GKvMGnTF</t>
         </is>
       </c>
-      <c r="B599" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C599" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D599" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="B599" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C599" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D599" t="n">
+        <v>2.45</v>
       </c>
     </row>
     <row r="600">
@@ -9413,20 +9125,14 @@
           <t>lhZp7ZeJ</t>
         </is>
       </c>
-      <c r="B600" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="C600" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D600" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B600" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C600" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D600" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="601">
@@ -9445,20 +9151,14 @@
           <t>l4qimuLi</t>
         </is>
       </c>
-      <c r="B602" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="C602" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D602" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
+      <c r="B602" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="C602" t="n">
+        <v>4</v>
+      </c>
+      <c r="D602" t="n">
+        <v>1.67</v>
       </c>
     </row>
     <row r="603">
@@ -9467,20 +9167,14 @@
           <t>6oqDlq2D</t>
         </is>
       </c>
-      <c r="B603" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C603" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D603" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
+      <c r="B603" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C603" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D603" t="n">
+        <v>2.38</v>
       </c>
     </row>
     <row r="604">
@@ -9489,20 +9183,14 @@
           <t>xnTEulJr</t>
         </is>
       </c>
-      <c r="B604" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C604" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D604" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B604" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C604" t="n">
+        <v>4</v>
+      </c>
+      <c r="D604" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="605">
@@ -9511,20 +9199,14 @@
           <t>dUnaoJk4</t>
         </is>
       </c>
-      <c r="B605" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="C605" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D605" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B605" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C605" t="n">
+        <v>4</v>
+      </c>
+      <c r="D605" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="606">
@@ -9533,20 +9215,14 @@
           <t>4AGA85Er</t>
         </is>
       </c>
-      <c r="B606" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="C606" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D606" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B606" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C606" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D606" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="607">
@@ -9555,20 +9231,14 @@
           <t>xnkMDjsm</t>
         </is>
       </c>
-      <c r="B607" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C607" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D607" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="B607" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C607" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D607" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="608">
@@ -9577,20 +9247,14 @@
           <t>x8QdQTQh</t>
         </is>
       </c>
-      <c r="B608" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="C608" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D608" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
+      <c r="B608" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C608" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D608" t="n">
+        <v>1.42</v>
       </c>
     </row>
     <row r="609">
@@ -9599,20 +9263,14 @@
           <t>Sti6DhR6</t>
         </is>
       </c>
-      <c r="B609" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C609" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D609" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B609" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C609" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D609" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="610">
@@ -9621,20 +9279,14 @@
           <t>t62SsD9M</t>
         </is>
       </c>
-      <c r="B610" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C610" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D610" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="B610" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C610" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D610" t="n">
+        <v>3.25</v>
       </c>
     </row>
     <row r="611">
@@ -9643,20 +9295,14 @@
           <t>YJDXTDBm</t>
         </is>
       </c>
-      <c r="B611" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="C611" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D611" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="B611" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C611" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D611" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="612">
@@ -9665,20 +9311,14 @@
           <t>AP8dO9uP</t>
         </is>
       </c>
-      <c r="B612" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="C612" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D612" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
+      <c r="B612" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C612" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D612" t="n">
+        <v>1.65</v>
       </c>
     </row>
     <row r="613">
@@ -9687,20 +9327,14 @@
           <t>2NJCQaMh</t>
         </is>
       </c>
-      <c r="B613" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C613" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D613" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B613" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C613" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D613" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="614">
@@ -9709,20 +9343,14 @@
           <t>QwvaxiXq</t>
         </is>
       </c>
-      <c r="B614" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C614" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D614" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B614" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C614" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D614" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="615">
@@ -9731,20 +9359,14 @@
           <t>bkDLOwi5</t>
         </is>
       </c>
-      <c r="B615" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C615" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D615" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="B615" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C615" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D615" t="n">
+        <v>2.75</v>
       </c>
     </row>
     <row r="616">
@@ -9753,20 +9375,14 @@
           <t>G2X0ZZmQ</t>
         </is>
       </c>
-      <c r="B616" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="C616" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D616" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
+      <c r="B616" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C616" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D616" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="617">
@@ -9775,20 +9391,14 @@
           <t>6XBuSit0</t>
         </is>
       </c>
-      <c r="B617" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C617" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D617" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B617" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C617" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D617" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="618">
@@ -9797,20 +9407,14 @@
           <t>2a5lQVAC</t>
         </is>
       </c>
-      <c r="B618" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C618" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D618" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="B618" t="n">
+        <v>3</v>
+      </c>
+      <c r="C618" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D618" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="619">
@@ -9819,19 +9423,165 @@
           <t>lduFBWeJ</t>
         </is>
       </c>
-      <c r="B619" t="inlineStr">
+      <c r="B619" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C619" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D619" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="inlineStr">
+        <is>
+          <t>Of1jzRNE</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="inlineStr">
+        <is>
+          <t>AFJ3CNV7</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="inlineStr">
+        <is>
+          <t>AVat9lPF</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
         <is>
           <t>3.10</t>
         </is>
       </c>
-      <c r="C619" t="inlineStr">
+      <c r="C622" t="inlineStr">
         <is>
           <t>3.60</t>
         </is>
       </c>
-      <c r="D619" t="inlineStr">
-        <is>
-          <t>2.15</t>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="inlineStr">
+        <is>
+          <t>KAYsYMjm</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t>Ox4C03W7</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr"/>
+      <c r="C624" t="inlineStr"/>
+      <c r="D624" t="inlineStr"/>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t>2XhHz2yn</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>0ARSCwSs</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr"/>
+      <c r="C626" t="inlineStr"/>
+      <c r="D626" t="inlineStr"/>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>G6L4SLit</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>1.85</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D163"/>
+  <dimension ref="A1:D650"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4009,6 +4009,8848 @@
         </is>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>tYjCfe2E</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>zwcBwqTP</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>r5DHBTv9</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>Kp7e4oXr</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>MZUbUvjC</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>SzxjW0La</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>AyusUVeT</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>8UZIZZRi</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>xARZViRG</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>fqXMknIk</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>GbLVmQn2</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>4YtaO6OE</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>8W4PFuyJ</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>Oru43jUb</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>WthfvVyR</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>KAYsYMjm</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>Ox4C03W7</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
+          <t>2XhHz2yn</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>0ARSCwSs</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>GbRWUxlQ</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>WCpYWJzB</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>OhdEZ36b</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>I9KbIKLH</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>lrh6iw43</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>bcLO4xyD</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>K4VeyRD5</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>YwdQcmuR</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>I5AeSkdt</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>vXfNMRbC</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="inlineStr">
+        <is>
+          <t>jaUqrSMj</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="inlineStr">
+        <is>
+          <t>MHsUEQcS</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="inlineStr">
+        <is>
+          <t>KCsUAHdf</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="inlineStr">
+        <is>
+          <t>WW4IdRyp</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>pIFVy6I7</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t>IsdlPSY1</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="inlineStr">
+        <is>
+          <t>WlblghVi</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr"/>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>WWGbDMV6</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>MLqiJCJP</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>KhoDI8b3</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>Sxox9eR6</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>fTrEmlaT</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>0MBBVesp</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>6kJ094Lk</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>WnwqL71s</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>lUSsM2Mh</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>0Uk5kAUG</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr"/>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>zalWK5TO</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>YRgnVhvd</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>SAhNinbn</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr"/>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="inlineStr">
+        <is>
+          <t>zRfR2QoD</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>UN4eVor9</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>pdMjKti5</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>dWHRJCuP</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr"/>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>2DUZNOit</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>KQM2PGBm</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>SvvsVc5N</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>0QcIa9AE</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>SbbRf56d</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>pWf4j5X0</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>6RtwA8tC</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>EXFv49qA</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>b1HNwSme</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>Or3uRl4k</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr"/>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>hOxchR2l</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr"/>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>6mIDMoQH</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>l6EJLYAC</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>zm4m2mEM</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>EFM87rj2</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>2issnpX7</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr"/>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>z5NkFr1f</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr"/>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>OnsQYu6b</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>EyE7GbjU</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>Y7eVkQSb</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>b1wVBUBa</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr"/>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>67CW5VEc</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr"/>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>h4nciWa4</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>OAPCPyTp</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr"/>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>Iqy8qcKG</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>GWO4Z4rI</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>2gzn8nBO</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>MN2wyBFN</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>WIaMXsyB</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr"/>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>4r62Vlwo</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>xAePbNGD</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr"/>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>63xqoAeL</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr"/>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>hvLANft0</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>0E33lZ3q</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>GKvMGnTF</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>lhZp7ZeJ</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>AyqzmWQ8</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr"/>
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>l4qimuLi</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>6oqDlq2D</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>xnTEulJr</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>dUnaoJk4</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>4AGA85Er</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>xnkMDjsm</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>x8QdQTQh</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>vVFzzC2U</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>Khe3WoFL</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>h0rLgzUq</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr"/>
+      <c r="C263" t="inlineStr"/>
+      <c r="D263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>nqgAsXvK</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr"/>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>KGwjNsx8</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr"/>
+      <c r="C265" t="inlineStr"/>
+      <c r="D265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>QXEgHUR7</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr"/>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>n3urP37e</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr"/>
+      <c r="C267" t="inlineStr"/>
+      <c r="D267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>fk6OJTnD</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr"/>
+      <c r="C268" t="inlineStr"/>
+      <c r="D268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>0SUSUgeE</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>KzpTUYwH</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr"/>
+      <c r="C270" t="inlineStr"/>
+      <c r="D270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>8foZ2v7c</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr"/>
+      <c r="C271" t="inlineStr"/>
+      <c r="D271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>nk09A4h2</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr"/>
+      <c r="C272" t="inlineStr"/>
+      <c r="D272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>bw7fY7p9</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>Sb8nuyFj</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>jN60CQNk</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>jynZQPxq</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>dUdkad6M</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr"/>
+      <c r="C277" t="inlineStr"/>
+      <c r="D277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>QDOgGZON</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr"/>
+      <c r="C278" t="inlineStr"/>
+      <c r="D278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>hQ97NBml</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr"/>
+      <c r="C279" t="inlineStr"/>
+      <c r="D279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>0jDFLkI0</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr"/>
+      <c r="C280" t="inlineStr"/>
+      <c r="D280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>UoVpIefB</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr"/>
+      <c r="C281" t="inlineStr"/>
+      <c r="D281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>dGHGpciT</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr"/>
+      <c r="C282" t="inlineStr"/>
+      <c r="D282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>UNGpRiG6</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>8hYzTXPQ</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr"/>
+      <c r="C284" t="inlineStr"/>
+      <c r="D284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>jgmMIs3C</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr"/>
+      <c r="C285" t="inlineStr"/>
+      <c r="D285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>O8jKWf94</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr"/>
+      <c r="C286" t="inlineStr"/>
+      <c r="D286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>ddFPADno</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr"/>
+      <c r="C287" t="inlineStr"/>
+      <c r="D287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>xhhCYGvh</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr"/>
+      <c r="C288" t="inlineStr"/>
+      <c r="D288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>SWRIzxdS</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr"/>
+      <c r="C289" t="inlineStr"/>
+      <c r="D289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>hEytAlL6</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr"/>
+      <c r="C290" t="inlineStr"/>
+      <c r="D290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>IkSxE8Dt</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr"/>
+      <c r="C291" t="inlineStr"/>
+      <c r="D291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>AqLzFcCb</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr"/>
+      <c r="C292" t="inlineStr"/>
+      <c r="D292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>6kw90bc5</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr"/>
+      <c r="C293" t="inlineStr"/>
+      <c r="D293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>jyz8Ixzp</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr"/>
+      <c r="C294" t="inlineStr"/>
+      <c r="D294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>KW71BLSG</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr"/>
+      <c r="C295" t="inlineStr"/>
+      <c r="D295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>4zQgCGV0</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr"/>
+      <c r="C296" t="inlineStr"/>
+      <c r="D296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>plYXBAjf</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr"/>
+      <c r="C297" t="inlineStr"/>
+      <c r="D297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>K8al4YeU</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr"/>
+      <c r="C298" t="inlineStr"/>
+      <c r="D298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>d6nbgHsC</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr"/>
+      <c r="C299" t="inlineStr"/>
+      <c r="D299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>E3bH2ZAd</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr"/>
+      <c r="C300" t="inlineStr"/>
+      <c r="D300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>hQRLDaJc</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr"/>
+      <c r="C301" t="inlineStr"/>
+      <c r="D301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>OSEc76Ak</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr"/>
+      <c r="C302" t="inlineStr"/>
+      <c r="D302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>rFdeX5Xp</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr"/>
+      <c r="C303" t="inlineStr"/>
+      <c r="D303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>GhQhDBYp</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr"/>
+      <c r="C304" t="inlineStr"/>
+      <c r="D304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>6BbKeRcC</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr"/>
+      <c r="C305" t="inlineStr"/>
+      <c r="D305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>v3yHbxSH</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr"/>
+      <c r="C306" t="inlineStr"/>
+      <c r="D306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>pvekOSfU</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>C4BrrfEE</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr"/>
+      <c r="C308" t="inlineStr"/>
+      <c r="D308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>IVsJZ1cE</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr"/>
+      <c r="C309" t="inlineStr"/>
+      <c r="D309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>Ot6u6fRH</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr"/>
+      <c r="C310" t="inlineStr"/>
+      <c r="D310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>ANq02KSh</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr"/>
+      <c r="C311" t="inlineStr"/>
+      <c r="D311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>Gb1A9acT</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr"/>
+      <c r="C312" t="inlineStr"/>
+      <c r="D312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>C43kVFJk</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr"/>
+      <c r="C313" t="inlineStr"/>
+      <c r="D313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>jXaKcHG7</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr"/>
+      <c r="C314" t="inlineStr"/>
+      <c r="D314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>KhqxObCM</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr"/>
+      <c r="C315" t="inlineStr"/>
+      <c r="D315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>K6OAxbRF</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr"/>
+      <c r="C316" t="inlineStr"/>
+      <c r="D316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>vcIeQx33</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr"/>
+      <c r="C317" t="inlineStr"/>
+      <c r="D317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>4Cs7LK8E</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>W61W8sP8</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr"/>
+      <c r="C319" t="inlineStr"/>
+      <c r="D319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>bJWjBFBN</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr"/>
+      <c r="C320" t="inlineStr"/>
+      <c r="D320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>j9HX6LgL</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr"/>
+      <c r="C321" t="inlineStr"/>
+      <c r="D321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>M5JxAHIM</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>C64gDsb4</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr"/>
+      <c r="C323" t="inlineStr"/>
+      <c r="D323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>xEisQlQH</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr"/>
+      <c r="C324" t="inlineStr"/>
+      <c r="D324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>4Wk6ieCO</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr"/>
+      <c r="C325" t="inlineStr"/>
+      <c r="D325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>WprGGG4d</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr"/>
+      <c r="C326" t="inlineStr"/>
+      <c r="D326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>tzIzWVsQ</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>vwhQPEQG</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr"/>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>vuaksbnB</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr"/>
+      <c r="C329" t="inlineStr"/>
+      <c r="D329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>0YJgAQC5</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr"/>
+      <c r="C330" t="inlineStr"/>
+      <c r="D330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>pbJdKjM7</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr"/>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>SQfscarm</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr"/>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>jqtRXuSQ</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr"/>
+      <c r="C333" t="inlineStr"/>
+      <c r="D333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>jT7X7Gd5</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr"/>
+      <c r="C334" t="inlineStr"/>
+      <c r="D334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>dIO7tAAb</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr"/>
+      <c r="C335" t="inlineStr"/>
+      <c r="D335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>WKO7Omz0</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>tj094etp</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr"/>
+      <c r="C337" t="inlineStr"/>
+      <c r="D337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>tr0QWSff</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr"/>
+      <c r="C338" t="inlineStr"/>
+      <c r="D338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>I9OrDysB</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr"/>
+      <c r="C339" t="inlineStr"/>
+      <c r="D339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>jDiLRtDc</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr"/>
+      <c r="C340" t="inlineStr"/>
+      <c r="D340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>6Xq5xjLq</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr"/>
+      <c r="C341" t="inlineStr"/>
+      <c r="D341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>ALlse9Pi</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr"/>
+      <c r="C342" t="inlineStr"/>
+      <c r="D342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>CpJVj93N</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>Mi831aHr</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr"/>
+      <c r="C344" t="inlineStr"/>
+      <c r="D344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>SnzzjdRj</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr"/>
+      <c r="C345" t="inlineStr"/>
+      <c r="D345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>8G41omRp</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr"/>
+      <c r="C346" t="inlineStr"/>
+      <c r="D346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>jHHGvluB</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr"/>
+      <c r="C347" t="inlineStr"/>
+      <c r="D347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>OvV1vKd3</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr"/>
+      <c r="C348" t="inlineStr"/>
+      <c r="D348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>f1EO9xSh</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr"/>
+      <c r="C349" t="inlineStr"/>
+      <c r="D349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>IBytSAe5</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr"/>
+      <c r="C350" t="inlineStr"/>
+      <c r="D350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>bweTPKsA</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr"/>
+      <c r="C351" t="inlineStr"/>
+      <c r="D351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>lUWRGJsn</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr"/>
+      <c r="C352" t="inlineStr"/>
+      <c r="D352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>GIPMhVYA</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr"/>
+      <c r="C353" t="inlineStr"/>
+      <c r="D353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>ATMcSJkl</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr"/>
+      <c r="C354" t="inlineStr"/>
+      <c r="D354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>OUFOxS9N</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>roLym02k</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr"/>
+      <c r="C356" t="inlineStr"/>
+      <c r="D356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>pbwYTWQh</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr"/>
+      <c r="C357" t="inlineStr"/>
+      <c r="D357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>Wzwjgmf4</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr"/>
+      <c r="C358" t="inlineStr"/>
+      <c r="D358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>GW4e7Um4</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr"/>
+      <c r="C359" t="inlineStr"/>
+      <c r="D359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>EuGUBwlA</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr"/>
+      <c r="C360" t="inlineStr"/>
+      <c r="D360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>8pGGBbct</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr"/>
+      <c r="C361" t="inlineStr"/>
+      <c r="D361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2yu5QcK0</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr"/>
+      <c r="C362" t="inlineStr"/>
+      <c r="D362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>ltVl8SkJ</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr"/>
+      <c r="C363" t="inlineStr"/>
+      <c r="D363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>OrVmMCie</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr"/>
+      <c r="C364" t="inlineStr"/>
+      <c r="D364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>b5iIdGdU</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr"/>
+      <c r="C365" t="inlineStr"/>
+      <c r="D365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>Ac09TdRi</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr"/>
+      <c r="C366" t="inlineStr"/>
+      <c r="D366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t>Ey2Sg5SO</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr"/>
+      <c r="C367" t="inlineStr"/>
+      <c r="D367" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="inlineStr">
+        <is>
+          <t>ETqpict9</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr"/>
+      <c r="C368" t="inlineStr"/>
+      <c r="D368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="1" t="inlineStr">
+        <is>
+          <t>GUs6MFBb</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr"/>
+      <c r="C369" t="inlineStr"/>
+      <c r="D369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="inlineStr">
+        <is>
+          <t>dAMoEx1l</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr"/>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t>xng458IG</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr"/>
+      <c r="C371" t="inlineStr"/>
+      <c r="D371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t>0fDYRkv8</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr"/>
+      <c r="C372" t="inlineStr"/>
+      <c r="D372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>CUnt4wLj</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr"/>
+      <c r="C373" t="inlineStr"/>
+      <c r="D373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>fkIM5gZp</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>r7dCawne</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr"/>
+      <c r="C375" t="inlineStr"/>
+      <c r="D375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>xQuFJbwR</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr"/>
+      <c r="C376" t="inlineStr"/>
+      <c r="D376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>46QpCnrg</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr"/>
+      <c r="C377" t="inlineStr"/>
+      <c r="D377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>OjTDOykD</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr"/>
+      <c r="C378" t="inlineStr"/>
+      <c r="D378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>OOnl9jJi</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr"/>
+      <c r="C379" t="inlineStr"/>
+      <c r="D379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>YoI184sI</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr"/>
+      <c r="C380" t="inlineStr"/>
+      <c r="D380" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>EwFQTB9e</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr"/>
+      <c r="C381" t="inlineStr"/>
+      <c r="D381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>zgw9F7bE</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>hzDGMR4C</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr"/>
+      <c r="C383" t="inlineStr"/>
+      <c r="D383" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>0vgkewDa</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr"/>
+      <c r="C384" t="inlineStr"/>
+      <c r="D384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>KMvNIXAN</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr"/>
+      <c r="C385" t="inlineStr"/>
+      <c r="D385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>pG6HYlQs</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr"/>
+      <c r="C386" t="inlineStr"/>
+      <c r="D386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="inlineStr">
+        <is>
+          <t>lhLarWun</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="inlineStr">
+        <is>
+          <t>OfoEKgtB</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr"/>
+      <c r="C388" t="inlineStr"/>
+      <c r="D388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="inlineStr">
+        <is>
+          <t>bZvl4Jlo</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr"/>
+      <c r="C389" t="inlineStr"/>
+      <c r="D389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="inlineStr">
+        <is>
+          <t>lWqPVhdt</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr"/>
+      <c r="C390" t="inlineStr"/>
+      <c r="D390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="inlineStr">
+        <is>
+          <t>OfLaQ95m</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr"/>
+      <c r="C391" t="inlineStr"/>
+      <c r="D391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="inlineStr">
+        <is>
+          <t>fFgcOysn</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr"/>
+      <c r="C392" t="inlineStr"/>
+      <c r="D392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="inlineStr">
+        <is>
+          <t>QkE2Af0D</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr"/>
+      <c r="C393" t="inlineStr"/>
+      <c r="D393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>2cth4tbt</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr"/>
+      <c r="C394" t="inlineStr"/>
+      <c r="D394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="inlineStr">
+        <is>
+          <t>Ma8YsCcM</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr"/>
+      <c r="C395" t="inlineStr"/>
+      <c r="D395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="inlineStr">
+        <is>
+          <t>bL1cTgl2</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr"/>
+      <c r="C396" t="inlineStr"/>
+      <c r="D396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="inlineStr">
+        <is>
+          <t>IN3HRzd4</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr"/>
+      <c r="C397" t="inlineStr"/>
+      <c r="D397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="inlineStr">
+        <is>
+          <t>OYqPDWLs</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr"/>
+      <c r="C398" t="inlineStr"/>
+      <c r="D398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="inlineStr">
+        <is>
+          <t>fJggJhbK</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr"/>
+      <c r="C399" t="inlineStr"/>
+      <c r="D399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="inlineStr">
+        <is>
+          <t>vDEpovX1</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="1" t="inlineStr">
+        <is>
+          <t>b9LHre3B</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="inlineStr">
+        <is>
+          <t>xU5RBAXB</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="inlineStr">
+        <is>
+          <t>GK4VAUnI</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="inlineStr">
+        <is>
+          <t>pClG5zQ1</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="inlineStr">
+        <is>
+          <t>KU4yDIXR</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="inlineStr">
+        <is>
+          <t>Gza5n1kb</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="inlineStr">
+        <is>
+          <t>YyoC6GAe</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>A3eEI0Pp</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>4MvHxMGG</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>xAgY1xpS</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>21.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>dKJeVw9j</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>QyTPz0oT</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>CS1rgs1c</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>4deQ3bFF</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>pt0jiLV9</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>dfz5dG7k</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>hxlYyYo4</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>U32wGjPp</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>hGzqjO6E</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>OrHrRGXo</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>WQF2UUMt</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>rkazN4LU</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>GEugARyP</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>Wn71woN8</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>EkqxE9x0</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>dUjtW2Fr</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>MFnpCm7C</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>UsklUtpe</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>ddFjPf2b</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>Sh9BS8ig</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>dAfPwfHi</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>pWQ6LC1N</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>jiUEFsV1</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>dY0SOQjI</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>hO8aNYWA</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>vDA9yPiL</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>hzeTFV7m</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>Q9rcSKE7</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>zJCJQnM5</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>QkntzCGG</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>rRQ6H30k</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>697ha3El</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>634r8bcJ</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>pbFTwdnB</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>vyoZBtbf</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>CnnJp4ae</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>bw1zAKS6</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>GINCsvmn</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>x6klsVh3</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="inlineStr">
+        <is>
+          <t>b3pRrrU7</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="inlineStr">
+        <is>
+          <t>WfkfPdXH</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>SMr3Nz2U</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>xYBLuIHb</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>6os5wmhS</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>Kl7vhn7L</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>nw6fJO5K</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>bHPacsq1</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>MwmHgKaN</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>lQl9etVA</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>KWD8eLDD</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="inlineStr">
+        <is>
+          <t>xUXzYQFk</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="inlineStr">
+        <is>
+          <t>CCV9JR0d</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>bsinRI25</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="inlineStr">
+        <is>
+          <t>GbaVU03t</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="inlineStr">
+        <is>
+          <t>tOTmlbNp</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="inlineStr">
+        <is>
+          <t>nPQL4PjR</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="inlineStr">
+        <is>
+          <t>pWhdu9NF</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="inlineStr">
+        <is>
+          <t>6NnRD2Ts</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="inlineStr">
+        <is>
+          <t>2FcwTvYh</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="inlineStr">
+        <is>
+          <t>EBSD6oME</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>WSQqW4p2</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>vaX1LmWq</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>n1hhaOVo</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>OMDVg8x9</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="inlineStr">
+        <is>
+          <t>jXcAnQUr</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="inlineStr">
+        <is>
+          <t>fRe0c20b</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="inlineStr">
+        <is>
+          <t>G6L4SLit</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="inlineStr">
+        <is>
+          <t>Sti6DhR6</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="inlineStr">
+        <is>
+          <t>t62SsD9M</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="inlineStr">
+        <is>
+          <t>YJDXTDBm</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="inlineStr">
+        <is>
+          <t>AP8dO9uP</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="1" t="inlineStr">
+        <is>
+          <t>2NJCQaMh</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="inlineStr">
+        <is>
+          <t>QwvaxiXq</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="inlineStr">
+        <is>
+          <t>bkDLOwi5</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="inlineStr">
+        <is>
+          <t>G2X0ZZmQ</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="inlineStr">
+        <is>
+          <t>6XBuSit0</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="inlineStr">
+        <is>
+          <t>2a5lQVAC</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr">
+        <is>
+          <t>lduFBWeJ</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>KGmbFEdf</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>82DqAJKE</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>4U6h8ckR</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>faoX0Fs1</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>2PluagCD</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>IXWRMd4K</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>E3IcHzSs</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="inlineStr">
+        <is>
+          <t>YuaKqZvA</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>KtXllxbe</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>xE5BoeAc</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>G8QcnGS7</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>YqcO2yDl</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>pKIPNiIj</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>23e0sUpB</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>prkJckVi</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>6cwSeTa4</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>ENtzf7UG</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>6BI0ASEc</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>EyM886qA</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>YPYtjbTr</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>zHg8u8FN</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>IycXZowo</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>fXlrhoaT</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>j3zEnPMj</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>fcYYQ80U</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>vm3yIDHa</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>KxZpVZPG</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>Ohp1YY1t</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>KKwAWCWh</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>l0VQSUVH</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>S2xgTDfT</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>bBbqoCon</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>8SfhEVGO</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>hYyIUj15</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>6y2iqjGb</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>nD6qGinC</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>4xLQ2Sg5</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>WOMI4lPh</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>8UHsapgU</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2meCcXHP</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>bJtrhBum</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>CrrhJmvn</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>ILdqjkAa</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>Qo0ilTvC</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>n1l0n79O</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>xQT96Aft</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>04EZ06OH</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="inlineStr">
+        <is>
+          <t>pCQRkLbJ</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="inlineStr">
+        <is>
+          <t>YJBMWNJa</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="inlineStr">
+        <is>
+          <t>INcgaD7l</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="inlineStr">
+        <is>
+          <t>pzkAeV6D</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="inlineStr">
+        <is>
+          <t>bwHM4ZqR</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="1" t="inlineStr">
+        <is>
+          <t>OK01cix1</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="inlineStr">
+        <is>
+          <t>4WLAk4Z3</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>IZPElOlA</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>0bFJmr4G</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="inlineStr">
+        <is>
+          <t>vkENn2JM</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="inlineStr">
+        <is>
+          <t>8OIRoMYS</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="inlineStr">
+        <is>
+          <t>AX4gstsp</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>hdfbt0dj</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="inlineStr">
+        <is>
+          <t>6FvA8wct</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>jsD1uKBd</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>4p1q43lc</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>zkqE7cCn</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>ry0m3N33</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>dpLdP7Lb</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>zeWeY24T</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>vTxmzPZG</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>hCzywRkb</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>W2Zvxo54</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>21EalzCO</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>0xvqy5KA</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>MiSiZrkN</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>46hrDJlP</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>WQHRStSj</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>WIN2iQ4i</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>A9M6jpKc</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>hzJNTMCp</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>ChwTrK5K</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>4jI7yxbf</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="inlineStr">
+        <is>
+          <t>hCE5NojB</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="inlineStr">
+        <is>
+          <t>IgMhQm6h</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="inlineStr">
+        <is>
+          <t>QPCDLPKN</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>fyBijdsC</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="inlineStr">
+        <is>
+          <t>lbAekGdI</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="inlineStr">
+        <is>
+          <t>nZD9M55H</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="inlineStr">
+        <is>
+          <t>r17IKqzU</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="inlineStr">
+        <is>
+          <t>pAgpG3ro</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="1" t="inlineStr">
+        <is>
+          <t>bDsSvmLo</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="1" t="inlineStr">
+        <is>
+          <t>AmoWw7zh</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="1" t="inlineStr">
+        <is>
+          <t>v9A1ORz5</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="1" t="inlineStr">
+        <is>
+          <t>COF1M5hj</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="1" t="inlineStr">
+        <is>
+          <t>YkKnUd7Q</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="1" t="inlineStr">
+        <is>
+          <t>8rBEPGFs</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="1" t="inlineStr">
+        <is>
+          <t>25AIOzVm</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="1" t="inlineStr">
+        <is>
+          <t>td9MNfpf</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="1" t="inlineStr">
+        <is>
+          <t>lOuihICa</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="1" t="inlineStr">
+        <is>
+          <t>Wp2ZKhUC</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="1" t="inlineStr">
+        <is>
+          <t>pl6wKCqJ</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="inlineStr">
+        <is>
+          <t>pS8oS9yt</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="1" t="inlineStr">
+        <is>
+          <t>GpCmixS5</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="1" t="inlineStr">
+        <is>
+          <t>OI7kRTjn</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="1" t="inlineStr">
+        <is>
+          <t>bX3RMEa0</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="inlineStr">
+        <is>
+          <t>xO2VLYE6</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="1" t="inlineStr">
+        <is>
+          <t>AXtmgbcg</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="1" t="inlineStr">
+        <is>
+          <t>jRUsVxhK</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="1" t="inlineStr">
+        <is>
+          <t>GAsqfvrm</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="1" t="inlineStr">
+        <is>
+          <t>pUwh8Fp7</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="1" t="inlineStr">
+        <is>
+          <t>OKxd7ZaD</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="1" t="inlineStr">
+        <is>
+          <t>CzWwWIxE</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="1" t="inlineStr">
+        <is>
+          <t>YTrCHJNK</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="1" t="inlineStr">
+        <is>
+          <t>CKsGGwwR</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="1" t="inlineStr">
+        <is>
+          <t>GlnyCcor</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="inlineStr">
+        <is>
+          <t>fuouBH0l</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="1" t="inlineStr">
+        <is>
+          <t>l2pqAyGf</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1" t="inlineStr">
+        <is>
+          <t>25lm9eV0</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="1" t="inlineStr">
+        <is>
+          <t>f5UVqu2k</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="inlineStr">
+        <is>
+          <t>dQ0Ca0KP</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="1" t="inlineStr">
+        <is>
+          <t>jXNvrJW1</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="1" t="inlineStr">
+        <is>
+          <t>rRAQ5MO8</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="1" t="inlineStr">
+        <is>
+          <t>025V4tvF</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="1" t="inlineStr">
+        <is>
+          <t>27wueKSt</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="inlineStr">
+        <is>
+          <t>xra9cbWl</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="inlineStr">
+        <is>
+          <t>Ob1LfdG7</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="1" t="inlineStr">
+        <is>
+          <t>Q3u4Jug8</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="inlineStr">
+        <is>
+          <t>v7q8Ia8E</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="inlineStr">
+        <is>
+          <t>YF3w3K8R</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="1" t="inlineStr">
+        <is>
+          <t>GYcDdIoe</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="inlineStr">
+        <is>
+          <t>zcgGkAYA</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="1" t="inlineStr">
+        <is>
+          <t>SWk8iW3b</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="1" t="inlineStr">
+        <is>
+          <t>6H1aghZo</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="inlineStr">
+        <is>
+          <t>UJ8QycSI</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="inlineStr">
+        <is>
+          <t>SUAlX1Iq</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="inlineStr">
+        <is>
+          <t>0r9dVumd</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="inlineStr">
+        <is>
+          <t>x0hufPPd</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t>ADjmh3f9</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t>OGfiiN9F</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>IZ180t5J</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>pWr0k1vS</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>ILrLlUmH</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t>hEcefYJu</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t>l2WgmZd6</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t>84KHwJc6</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>YkY5pXtP</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t>YZeQtFkt</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>OOlwvDZb</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t>xShswXl5</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>AuikyBJH</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>jT9MxwDC</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>x2NozVYN</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>290UuZ4n</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t>ShVcngCC</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t>8OObwbTs</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t>C2tsLGDD</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t>6FxXsvLQ</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t>CGLFZFS6</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t>fuBKYZsD</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t>0xb6dwzK</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>vTdAeckQ</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>bDwsjyDm</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>WQyklFs0</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>dUGDvar0</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D672"/>
+  <dimension ref="A1:D678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9899,20 +9899,14 @@
           <t>UwFBuMaf</t>
         </is>
       </c>
-      <c r="B651" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C651" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D651" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B651" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C651" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D651" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="652">
@@ -9921,20 +9915,14 @@
           <t>GhtVSrGl</t>
         </is>
       </c>
-      <c r="B652" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C652" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D652" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B652" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C652" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D652" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="653">
@@ -9943,20 +9931,14 @@
           <t>OIqwRMp1</t>
         </is>
       </c>
-      <c r="B653" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="C653" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D653" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="B653" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C653" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D653" t="n">
+        <v>2.45</v>
       </c>
     </row>
     <row r="654">
@@ -9965,20 +9947,14 @@
           <t>d8abY4hR</t>
         </is>
       </c>
-      <c r="B654" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C654" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D654" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B654" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C654" t="n">
+        <v>4</v>
+      </c>
+      <c r="D654" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="655">
@@ -9987,20 +9963,14 @@
           <t>pYXoP0FD</t>
         </is>
       </c>
-      <c r="B655" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="C655" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D655" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="B655" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C655" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D655" t="n">
+        <v>2.4</v>
       </c>
     </row>
     <row r="656">
@@ -10009,20 +9979,14 @@
           <t>xtzXn47K</t>
         </is>
       </c>
-      <c r="B656" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C656" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D656" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="B656" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C656" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D656" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="657">
@@ -10031,20 +9995,14 @@
           <t>dQG3srVs</t>
         </is>
       </c>
-      <c r="B657" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="C657" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="D657" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
+      <c r="B657" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C657" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D657" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="658">
@@ -10053,20 +10011,14 @@
           <t>Q58Kw0U6</t>
         </is>
       </c>
-      <c r="B658" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C658" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D658" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
+      <c r="B658" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C658" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D658" t="n">
+        <v>2.88</v>
       </c>
     </row>
     <row r="659">
@@ -10075,20 +10027,14 @@
           <t>W2BSyvaJ</t>
         </is>
       </c>
-      <c r="B659" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="C659" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D659" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="B659" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C659" t="n">
+        <v>5</v>
+      </c>
+      <c r="D659" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="660">
@@ -10097,20 +10043,14 @@
           <t>C0axT3Xo</t>
         </is>
       </c>
-      <c r="B660" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="C660" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D660" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
+      <c r="B660" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C660" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D660" t="n">
+        <v>1.95</v>
       </c>
     </row>
     <row r="661">
@@ -10119,20 +10059,14 @@
           <t>6XR3OUdM</t>
         </is>
       </c>
-      <c r="B661" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C661" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D661" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="B661" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C661" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D661" t="n">
+        <v>2.4</v>
       </c>
     </row>
     <row r="662">
@@ -10141,20 +10075,14 @@
           <t>W2BTMHLH</t>
         </is>
       </c>
-      <c r="B662" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C662" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D662" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="B662" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C662" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D662" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="663">
@@ -10163,20 +10091,14 @@
           <t>Q3T1495j</t>
         </is>
       </c>
-      <c r="B663" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="C663" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D663" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
+      <c r="B663" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C663" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D663" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="664">
@@ -10185,20 +10107,14 @@
           <t>Cfx7zV1d</t>
         </is>
       </c>
-      <c r="B664" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="C664" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D664" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
+      <c r="B664" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C664" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D664" t="n">
+        <v>1.62</v>
       </c>
     </row>
     <row r="665">
@@ -10207,20 +10123,14 @@
           <t>S2KgbYg3</t>
         </is>
       </c>
-      <c r="B665" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C665" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D665" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="B665" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C665" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D665" t="n">
+        <v>3.9</v>
       </c>
     </row>
     <row r="666">
@@ -10229,20 +10139,14 @@
           <t>xhzmSCcc</t>
         </is>
       </c>
-      <c r="B666" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C666" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D666" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="B666" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C666" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D666" t="n">
+        <v>3.9</v>
       </c>
     </row>
     <row r="667">
@@ -10251,20 +10155,14 @@
           <t>bV6rHnkd</t>
         </is>
       </c>
-      <c r="B667" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C667" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D667" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="B667" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C667" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D667" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="668">
@@ -10273,20 +10171,14 @@
           <t>6g3vy8tS</t>
         </is>
       </c>
-      <c r="B668" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="C668" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D668" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
+      <c r="B668" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C668" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D668" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="669">
@@ -10295,20 +10187,14 @@
           <t>b7OeQjS9</t>
         </is>
       </c>
-      <c r="B669" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C669" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D669" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="B669" t="n">
+        <v>2</v>
+      </c>
+      <c r="C669" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D669" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="670">
@@ -10317,20 +10203,14 @@
           <t>QH8zJ8Kq</t>
         </is>
       </c>
-      <c r="B670" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C670" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D670" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B670" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C670" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D670" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="671">
@@ -10339,20 +10219,14 @@
           <t>pvFVxUBF</t>
         </is>
       </c>
-      <c r="B671" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C671" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D671" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="B671" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C671" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D671" t="n">
+        <v>2.55</v>
       </c>
     </row>
     <row r="672">
@@ -10361,19 +10235,145 @@
           <t>xEBNvjs3</t>
         </is>
       </c>
-      <c r="B672" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C672" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D672" t="inlineStr">
-        <is>
-          <t>3.40</t>
+      <c r="B672" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C672" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D672" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="inlineStr">
+        <is>
+          <t>4KwDffx2</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="inlineStr">
+        <is>
+          <t>bPy9vrn4</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>21.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="inlineStr">
+        <is>
+          <t>riAVsHhd</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="1" t="inlineStr">
+        <is>
+          <t>Ac2H5Kp3</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>41.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="1" t="inlineStr">
+        <is>
+          <t>2cr0t4Hi</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="inlineStr">
+        <is>
+          <t>jgVjka0M</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>1.42</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D678"/>
+  <dimension ref="A1:D734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10251,20 +10251,14 @@
           <t>4KwDffx2</t>
         </is>
       </c>
-      <c r="B673" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="C673" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="D673" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
+      <c r="B673" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C673" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D673" t="n">
+        <v>7.5</v>
       </c>
     </row>
     <row r="674">
@@ -10273,20 +10267,14 @@
           <t>bPy9vrn4</t>
         </is>
       </c>
-      <c r="B674" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
-      <c r="C674" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
-      </c>
-      <c r="D674" t="inlineStr">
-        <is>
-          <t>21.00</t>
-        </is>
+      <c r="B674" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="C674" t="n">
+        <v>11</v>
+      </c>
+      <c r="D674" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="675">
@@ -10295,20 +10283,14 @@
           <t>riAVsHhd</t>
         </is>
       </c>
-      <c r="B675" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="C675" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D675" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
+      <c r="B675" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C675" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D675" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="676">
@@ -10317,20 +10299,14 @@
           <t>Ac2H5Kp3</t>
         </is>
       </c>
-      <c r="B676" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="C676" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
-      </c>
-      <c r="D676" t="inlineStr">
-        <is>
-          <t>41.00</t>
-        </is>
+      <c r="B676" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C676" t="n">
+        <v>15</v>
+      </c>
+      <c r="D676" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="677">
@@ -10339,20 +10315,14 @@
           <t>2cr0t4Hi</t>
         </is>
       </c>
-      <c r="B677" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="C677" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
-      </c>
-      <c r="D677" t="inlineStr">
-        <is>
-          <t>17.00</t>
-        </is>
+      <c r="B677" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C677" t="n">
+        <v>10</v>
+      </c>
+      <c r="D677" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="678">
@@ -10361,19 +10331,1245 @@
           <t>jgVjka0M</t>
         </is>
       </c>
-      <c r="B678" t="inlineStr">
+      <c r="B678" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C678" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D678" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="1" t="inlineStr">
+        <is>
+          <t>K0JghK0c</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="inlineStr">
+        <is>
+          <t>GhdgPLWA</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
         <is>
           <t>7.50</t>
         </is>
       </c>
-      <c r="C678" t="inlineStr">
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="inlineStr">
+        <is>
+          <t>l6f1Na1N</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="1" t="inlineStr">
+        <is>
+          <t>WQcQHwPp</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="1" t="inlineStr">
+        <is>
+          <t>bXkCusHi</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="inlineStr">
+        <is>
+          <t>4hy7UG8j</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="inlineStr">
+        <is>
+          <t>8MkyzwoT</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="inlineStr">
+        <is>
+          <t>0Ei9MyY2</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="inlineStr">
+        <is>
+          <t>rTas7Uuh</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="inlineStr">
+        <is>
+          <t>UPZ7hVQb</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="1" t="inlineStr">
+        <is>
+          <t>zPRNPuie</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="inlineStr">
+        <is>
+          <t>MkDBaAbf</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="inlineStr">
+        <is>
+          <t>SlBjZEH8</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="1" t="inlineStr">
+        <is>
+          <t>EcoWEpWg</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="1" t="inlineStr">
+        <is>
+          <t>z1qyZqU8</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="1" t="inlineStr">
+        <is>
+          <t>b3dRq1rR</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="1" t="inlineStr">
+        <is>
+          <t>SKHfqRmo</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="1" t="inlineStr">
+        <is>
+          <t>GMD4OFmp</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="1" t="inlineStr">
+        <is>
+          <t>Gpl1M6p3</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="1" t="inlineStr">
+        <is>
+          <t>MkTOG61s</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="1" t="inlineStr">
+        <is>
+          <t>zeO4BBP1</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="1" t="inlineStr">
+        <is>
+          <t>fZscvu6l</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="1" t="inlineStr">
+        <is>
+          <t>EJM6RNFa</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="1" t="inlineStr">
+        <is>
+          <t>xIamkdK6</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="1" t="inlineStr">
+        <is>
+          <t>8veHKF2F</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="1" t="inlineStr">
+        <is>
+          <t>dvGWNJL7</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="1" t="inlineStr">
+        <is>
+          <t>rVUmmzkJ</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="1" t="inlineStr">
+        <is>
+          <t>rwwmB2VI</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="1" t="inlineStr">
+        <is>
+          <t>rD7AIOqS</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
         <is>
           <t>4.33</t>
         </is>
       </c>
-      <c r="D678" t="inlineStr">
-        <is>
-          <t>1.42</t>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="1" t="inlineStr">
+        <is>
+          <t>zm42KpFF</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="1" t="inlineStr">
+        <is>
+          <t>8x8WhvLs</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="1" t="inlineStr">
+        <is>
+          <t>zBnkBtx2</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="1" t="inlineStr">
+        <is>
+          <t>lzCCMgId</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="1" t="inlineStr">
+        <is>
+          <t>441uiIkf</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="1" t="inlineStr">
+        <is>
+          <t>2y3IoNDE</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="1" t="inlineStr">
+        <is>
+          <t>SpqsD27k</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="1" t="inlineStr">
+        <is>
+          <t>dbvEzc5D</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="1" t="inlineStr">
+        <is>
+          <t>8Aoafidn</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="1" t="inlineStr">
+        <is>
+          <t>j1y6xJz1</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="1" t="inlineStr">
+        <is>
+          <t>xfH0b0cK</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="1" t="inlineStr">
+        <is>
+          <t>vTUeDXfk</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="1" t="inlineStr">
+        <is>
+          <t>UgqQIgXR</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="1" t="inlineStr">
+        <is>
+          <t>xjwGj9eB</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="1" t="inlineStr">
+        <is>
+          <t>SbOFR1Mr</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="1" t="inlineStr">
+        <is>
+          <t>8EsqXNbL</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="1" t="inlineStr">
+        <is>
+          <t>0GI1dCOF</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="1" t="inlineStr">
+        <is>
+          <t>OUZ4iTQ8</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="1" t="inlineStr">
+        <is>
+          <t>KdTDk7eL</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="1" t="inlineStr">
+        <is>
+          <t>juKqpoJr</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="1" t="inlineStr">
+        <is>
+          <t>Cf8hrPme</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="1" t="inlineStr">
+        <is>
+          <t>0U3n46AE</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="1" t="inlineStr">
+        <is>
+          <t>hSrRdO2l</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="1" t="inlineStr">
+        <is>
+          <t>xxfAVo4k</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="1" t="inlineStr">
+        <is>
+          <t>WzmJTPY1</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="1" t="inlineStr">
+        <is>
+          <t>Ys2f2puR</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="1" t="inlineStr">
+        <is>
+          <t>pMLat3I7</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>1.91</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D734"/>
+  <dimension ref="A1:D738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10347,20 +10347,14 @@
           <t>K0JghK0c</t>
         </is>
       </c>
-      <c r="B679" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-      <c r="C679" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="D679" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
+      <c r="B679" t="n">
+        <v>8</v>
+      </c>
+      <c r="C679" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D679" t="n">
+        <v>1.33</v>
       </c>
     </row>
     <row r="680">
@@ -10369,20 +10363,14 @@
           <t>GhdgPLWA</t>
         </is>
       </c>
-      <c r="B680" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
-      <c r="C680" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-      <c r="D680" t="inlineStr">
-        <is>
-          <t>13.00</t>
-        </is>
+      <c r="B680" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C680" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D680" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="681">
@@ -10391,20 +10379,14 @@
           <t>l6f1Na1N</t>
         </is>
       </c>
-      <c r="B681" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C681" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D681" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B681" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C681" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D681" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="682">
@@ -10413,20 +10395,14 @@
           <t>WQcQHwPp</t>
         </is>
       </c>
-      <c r="B682" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C682" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D682" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="B682" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C682" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D682" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="683">
@@ -10435,20 +10411,14 @@
           <t>bXkCusHi</t>
         </is>
       </c>
-      <c r="B683" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="C683" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D683" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="B683" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C683" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D683" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="684">
@@ -10457,20 +10427,14 @@
           <t>4hy7UG8j</t>
         </is>
       </c>
-      <c r="B684" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="C684" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D684" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="B684" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C684" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D684" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="685">
@@ -10479,20 +10443,14 @@
           <t>8MkyzwoT</t>
         </is>
       </c>
-      <c r="B685" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="C685" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D685" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
+      <c r="B685" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C685" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D685" t="n">
+        <v>1.67</v>
       </c>
     </row>
     <row r="686">
@@ -10501,20 +10459,14 @@
           <t>0Ei9MyY2</t>
         </is>
       </c>
-      <c r="B686" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="C686" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D686" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
+      <c r="B686" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="C686" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D686" t="n">
+        <v>1.73</v>
       </c>
     </row>
     <row r="687">
@@ -10523,20 +10475,14 @@
           <t>rTas7Uuh</t>
         </is>
       </c>
-      <c r="B687" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="C687" t="inlineStr">
-        <is>
-          <t>4.80</t>
-        </is>
-      </c>
-      <c r="D687" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
+      <c r="B687" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="C687" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D687" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="688">
@@ -10545,20 +10491,14 @@
           <t>UPZ7hVQb</t>
         </is>
       </c>
-      <c r="B688" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="C688" t="inlineStr">
-        <is>
-          <t>8.50</t>
-        </is>
-      </c>
-      <c r="D688" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
+      <c r="B688" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C688" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D688" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="689">
@@ -10567,20 +10507,14 @@
           <t>zPRNPuie</t>
         </is>
       </c>
-      <c r="B689" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="C689" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D689" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
+      <c r="B689" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C689" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D689" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="690">
@@ -10589,20 +10523,14 @@
           <t>MkDBaAbf</t>
         </is>
       </c>
-      <c r="B690" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C690" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D690" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
+      <c r="B690" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C690" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D690" t="n">
+        <v>2.05</v>
       </c>
     </row>
     <row r="691">
@@ -10611,20 +10539,14 @@
           <t>SlBjZEH8</t>
         </is>
       </c>
-      <c r="B691" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="C691" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D691" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="B691" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C691" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D691" t="n">
+        <v>3.9</v>
       </c>
     </row>
     <row r="692">
@@ -10633,20 +10555,14 @@
           <t>EcoWEpWg</t>
         </is>
       </c>
-      <c r="B692" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="C692" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D692" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
+      <c r="B692" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C692" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D692" t="n">
+        <v>1.73</v>
       </c>
     </row>
     <row r="693">
@@ -10655,20 +10571,14 @@
           <t>z1qyZqU8</t>
         </is>
       </c>
-      <c r="B693" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="C693" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="D693" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
+      <c r="B693" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C693" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D693" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="694">
@@ -10677,20 +10587,14 @@
           <t>b3dRq1rR</t>
         </is>
       </c>
-      <c r="B694" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="C694" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D694" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
+      <c r="B694" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C694" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D694" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="695">
@@ -10699,20 +10603,14 @@
           <t>SKHfqRmo</t>
         </is>
       </c>
-      <c r="B695" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="C695" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D695" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="B695" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C695" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D695" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="696">
@@ -10721,20 +10619,14 @@
           <t>GMD4OFmp</t>
         </is>
       </c>
-      <c r="B696" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="C696" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D696" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="B696" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C696" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D696" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="697">
@@ -10743,20 +10635,14 @@
           <t>Gpl1M6p3</t>
         </is>
       </c>
-      <c r="B697" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C697" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D697" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="B697" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C697" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D697" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="698">
@@ -10765,20 +10651,14 @@
           <t>MkTOG61s</t>
         </is>
       </c>
-      <c r="B698" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="C698" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D698" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
+      <c r="B698" t="n">
+        <v>5</v>
+      </c>
+      <c r="C698" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D698" t="n">
+        <v>1.44</v>
       </c>
     </row>
     <row r="699">
@@ -10787,20 +10667,14 @@
           <t>zeO4BBP1</t>
         </is>
       </c>
-      <c r="B699" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="C699" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D699" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
+      <c r="B699" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C699" t="n">
+        <v>4</v>
+      </c>
+      <c r="D699" t="n">
+        <v>1.62</v>
       </c>
     </row>
     <row r="700">
@@ -10809,20 +10683,14 @@
           <t>fZscvu6l</t>
         </is>
       </c>
-      <c r="B700" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C700" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D700" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
+      <c r="B700" t="n">
+        <v>3</v>
+      </c>
+      <c r="C700" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D700" t="n">
+        <v>2.05</v>
       </c>
     </row>
     <row r="701">
@@ -10831,20 +10699,14 @@
           <t>EJM6RNFa</t>
         </is>
       </c>
-      <c r="B701" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="C701" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D701" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="B701" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C701" t="n">
+        <v>4</v>
+      </c>
+      <c r="D701" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="702">
@@ -10853,20 +10715,14 @@
           <t>xIamkdK6</t>
         </is>
       </c>
-      <c r="B702" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="C702" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="D702" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
+      <c r="B702" t="n">
+        <v>6</v>
+      </c>
+      <c r="C702" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D702" t="n">
+        <v>1.36</v>
       </c>
     </row>
     <row r="703">
@@ -10875,20 +10731,14 @@
           <t>8veHKF2F</t>
         </is>
       </c>
-      <c r="B703" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="C703" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D703" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
+      <c r="B703" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C703" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D703" t="n">
+        <v>1.91</v>
       </c>
     </row>
     <row r="704">
@@ -10897,20 +10747,14 @@
           <t>dvGWNJL7</t>
         </is>
       </c>
-      <c r="B704" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="C704" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="D704" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
+      <c r="B704" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="C704" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D704" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="705">
@@ -10919,20 +10763,14 @@
           <t>rVUmmzkJ</t>
         </is>
       </c>
-      <c r="B705" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="C705" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D705" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
+      <c r="B705" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C705" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D705" t="n">
+        <v>1.95</v>
       </c>
     </row>
     <row r="706">
@@ -10941,20 +10779,14 @@
           <t>rwwmB2VI</t>
         </is>
       </c>
-      <c r="B706" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C706" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D706" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="B706" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C706" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D706" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="707">
@@ -10963,20 +10795,14 @@
           <t>rD7AIOqS</t>
         </is>
       </c>
-      <c r="B707" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="C707" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D707" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B707" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C707" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D707" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="708">
@@ -10985,20 +10811,14 @@
           <t>zm42KpFF</t>
         </is>
       </c>
-      <c r="B708" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="C708" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D708" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
+      <c r="B708" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C708" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D708" t="n">
+        <v>1.91</v>
       </c>
     </row>
     <row r="709">
@@ -11007,20 +10827,14 @@
           <t>8x8WhvLs</t>
         </is>
       </c>
-      <c r="B709" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="C709" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D709" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
+      <c r="B709" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C709" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D709" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="710">
@@ -11029,20 +10843,14 @@
           <t>zBnkBtx2</t>
         </is>
       </c>
-      <c r="B710" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C710" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D710" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
+      <c r="B710" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C710" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D710" t="n">
+        <v>2.63</v>
       </c>
     </row>
     <row r="711">
@@ -11051,20 +10859,14 @@
           <t>lzCCMgId</t>
         </is>
       </c>
-      <c r="B711" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="C711" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D711" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
+      <c r="B711" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C711" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D711" t="n">
+        <v>1.7</v>
       </c>
     </row>
     <row r="712">
@@ -11073,20 +10875,14 @@
           <t>441uiIkf</t>
         </is>
       </c>
-      <c r="B712" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C712" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D712" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="B712" t="n">
+        <v>2</v>
+      </c>
+      <c r="C712" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D712" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="713">
@@ -11095,20 +10891,14 @@
           <t>2y3IoNDE</t>
         </is>
       </c>
-      <c r="B713" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C713" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D713" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="B713" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C713" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D713" t="n">
+        <v>2.4</v>
       </c>
     </row>
     <row r="714">
@@ -11117,20 +10907,14 @@
           <t>SpqsD27k</t>
         </is>
       </c>
-      <c r="B714" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="C714" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D714" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="B714" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C714" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D714" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="715">
@@ -11139,20 +10923,14 @@
           <t>dbvEzc5D</t>
         </is>
       </c>
-      <c r="B715" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C715" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D715" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="B715" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C715" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D715" t="n">
+        <v>2.4</v>
       </c>
     </row>
     <row r="716">
@@ -11161,20 +10939,14 @@
           <t>8Aoafidn</t>
         </is>
       </c>
-      <c r="B716" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="C716" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D716" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
+      <c r="B716" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C716" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D716" t="n">
+        <v>1.55</v>
       </c>
     </row>
     <row r="717">
@@ -11183,20 +10955,14 @@
           <t>j1y6xJz1</t>
         </is>
       </c>
-      <c r="B717" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="C717" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="D717" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
+      <c r="B717" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C717" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D717" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="718">
@@ -11205,20 +10971,14 @@
           <t>xfH0b0cK</t>
         </is>
       </c>
-      <c r="B718" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="C718" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D718" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B718" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C718" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D718" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="719">
@@ -11227,20 +10987,14 @@
           <t>vTUeDXfk</t>
         </is>
       </c>
-      <c r="B719" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="C719" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D719" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
+      <c r="B719" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C719" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D719" t="n">
+        <v>1.75</v>
       </c>
     </row>
     <row r="720">
@@ -11249,20 +11003,14 @@
           <t>UgqQIgXR</t>
         </is>
       </c>
-      <c r="B720" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="C720" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D720" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
+      <c r="B720" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C720" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D720" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="721">
@@ -11271,20 +11019,14 @@
           <t>xjwGj9eB</t>
         </is>
       </c>
-      <c r="B721" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C721" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D721" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="B721" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C721" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D721" t="n">
+        <v>2.55</v>
       </c>
     </row>
     <row r="722">
@@ -11293,20 +11035,14 @@
           <t>SbOFR1Mr</t>
         </is>
       </c>
-      <c r="B722" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="C722" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D722" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B722" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C722" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D722" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="723">
@@ -11315,20 +11051,14 @@
           <t>8EsqXNbL</t>
         </is>
       </c>
-      <c r="B723" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="C723" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D723" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
+      <c r="B723" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C723" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D723" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="724">
@@ -11337,20 +11067,14 @@
           <t>0GI1dCOF</t>
         </is>
       </c>
-      <c r="B724" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C724" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D724" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="B724" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C724" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D724" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="725">
@@ -11359,20 +11083,14 @@
           <t>OUZ4iTQ8</t>
         </is>
       </c>
-      <c r="B725" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C725" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D725" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B725" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C725" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D725" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="726">
@@ -11381,20 +11099,14 @@
           <t>KdTDk7eL</t>
         </is>
       </c>
-      <c r="B726" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C726" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D726" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B726" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C726" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D726" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="727">
@@ -11403,20 +11115,14 @@
           <t>juKqpoJr</t>
         </is>
       </c>
-      <c r="B727" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="C727" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D727" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="B727" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C727" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D727" t="n">
+        <v>3.9</v>
       </c>
     </row>
     <row r="728">
@@ -11425,20 +11131,14 @@
           <t>Cf8hrPme</t>
         </is>
       </c>
-      <c r="B728" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C728" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D728" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="B728" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C728" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D728" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="729">
@@ -11447,20 +11147,14 @@
           <t>0U3n46AE</t>
         </is>
       </c>
-      <c r="B729" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="C729" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D729" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
+      <c r="B729" t="n">
+        <v>4</v>
+      </c>
+      <c r="C729" t="n">
+        <v>4</v>
+      </c>
+      <c r="D729" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="730">
@@ -11469,20 +11163,14 @@
           <t>hSrRdO2l</t>
         </is>
       </c>
-      <c r="B730" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C730" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D730" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="B730" t="n">
+        <v>3</v>
+      </c>
+      <c r="C730" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D730" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="731">
@@ -11491,20 +11179,14 @@
           <t>xxfAVo4k</t>
         </is>
       </c>
-      <c r="B731" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C731" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D731" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="B731" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C731" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D731" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="732">
@@ -11513,20 +11195,14 @@
           <t>WzmJTPY1</t>
         </is>
       </c>
-      <c r="B732" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="C732" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D732" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="B732" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C732" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D732" t="n">
+        <v>2.45</v>
       </c>
     </row>
     <row r="733">
@@ -11535,20 +11211,14 @@
           <t>Ys2f2puR</t>
         </is>
       </c>
-      <c r="B733" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C733" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D733" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="B733" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C733" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D733" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="734">
@@ -11557,19 +11227,101 @@
           <t>pMLat3I7</t>
         </is>
       </c>
-      <c r="B734" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="C734" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D734" t="inlineStr">
-        <is>
-          <t>1.91</t>
+      <c r="B734" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C734" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D734" t="n">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="1" t="inlineStr">
+        <is>
+          <t>SCsTyaGG</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="1" t="inlineStr">
+        <is>
+          <t>KnvLwLo4</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="1" t="inlineStr">
+        <is>
+          <t>WlWOlmQN</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="1" t="inlineStr">
+        <is>
+          <t>drCAfjgS</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>2.70</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D779"/>
+  <dimension ref="A1:D818"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11675,20 +11675,14 @@
           <t>l0Zi1FqS</t>
         </is>
       </c>
-      <c r="B762" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="C762" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D762" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
+      <c r="B762" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C762" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D762" t="n">
+        <v>1.95</v>
       </c>
     </row>
     <row r="763">
@@ -11697,20 +11691,14 @@
           <t>SQM1jbV9</t>
         </is>
       </c>
-      <c r="B763" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="C763" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-      <c r="D763" t="inlineStr">
-        <is>
-          <t>13.00</t>
-        </is>
+      <c r="B763" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="C763" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D763" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="764">
@@ -11719,20 +11707,14 @@
           <t>bFdtqGNq</t>
         </is>
       </c>
-      <c r="B764" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C764" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D764" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B764" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C764" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D764" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="765">
@@ -11741,20 +11723,14 @@
           <t>YXAOeg7k</t>
         </is>
       </c>
-      <c r="B765" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="C765" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D765" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="B765" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C765" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D765" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="766">
@@ -11763,20 +11739,14 @@
           <t>tbEWgXy2</t>
         </is>
       </c>
-      <c r="B766" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="C766" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="D766" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
+      <c r="B766" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C766" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D766" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="767">
@@ -11785,20 +11755,14 @@
           <t>d6dJHzU8</t>
         </is>
       </c>
-      <c r="B767" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C767" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D767" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
+      <c r="B767" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C767" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D767" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="768">
@@ -11807,20 +11771,14 @@
           <t>r3Wq3yFF</t>
         </is>
       </c>
-      <c r="B768" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="C768" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D768" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
+      <c r="B768" t="n">
+        <v>5</v>
+      </c>
+      <c r="C768" t="n">
+        <v>4</v>
+      </c>
+      <c r="D768" t="n">
+        <v>1.67</v>
       </c>
     </row>
     <row r="769">
@@ -11829,20 +11787,14 @@
           <t>QDIO1Apo</t>
         </is>
       </c>
-      <c r="B769" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C769" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D769" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B769" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C769" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D769" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="770">
@@ -11851,20 +11803,14 @@
           <t>hKAAPDxh</t>
         </is>
       </c>
-      <c r="B770" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C770" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D770" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B770" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C770" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D770" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="771">
@@ -11873,20 +11819,14 @@
           <t>0jcRLVyH</t>
         </is>
       </c>
-      <c r="B771" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C771" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D771" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="B771" t="n">
+        <v>3</v>
+      </c>
+      <c r="C771" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D771" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="772">
@@ -11895,20 +11835,14 @@
           <t>hlx6EmUj</t>
         </is>
       </c>
-      <c r="B772" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C772" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D772" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
+      <c r="B772" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C772" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D772" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="773">
@@ -11917,20 +11851,14 @@
           <t>ddiq9k8L</t>
         </is>
       </c>
-      <c r="B773" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C773" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D773" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B773" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C773" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D773" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="774">
@@ -11939,20 +11867,14 @@
           <t>EgN0zVjA</t>
         </is>
       </c>
-      <c r="B774" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="C774" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D774" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="B774" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C774" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D774" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="775">
@@ -11961,20 +11883,14 @@
           <t>z9B9Y8LM</t>
         </is>
       </c>
-      <c r="B775" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C775" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D775" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B775" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C775" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D775" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="776">
@@ -11983,20 +11899,14 @@
           <t>6Tyh7WMN</t>
         </is>
       </c>
-      <c r="B776" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C776" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D776" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B776" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C776" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D776" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="777">
@@ -12005,20 +11915,14 @@
           <t>EZbJNi74</t>
         </is>
       </c>
-      <c r="B777" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C777" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D777" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="B777" t="n">
+        <v>2</v>
+      </c>
+      <c r="C777" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D777" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="778">
@@ -12027,20 +11931,14 @@
           <t>dIjzK96T</t>
         </is>
       </c>
-      <c r="B778" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C778" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D778" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="B778" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C778" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D778" t="n">
+        <v>2.75</v>
       </c>
     </row>
     <row r="779">
@@ -12049,19 +11947,859 @@
           <t>8dKhxiMc</t>
         </is>
       </c>
-      <c r="B779" t="inlineStr">
+      <c r="B779" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C779" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D779" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="1" t="inlineStr">
+        <is>
+          <t>fsjksfhd</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="1" t="inlineStr">
+        <is>
+          <t>ltBAlx0M</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="1" t="inlineStr">
+        <is>
+          <t>nywy5cp3</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="1" t="inlineStr">
+        <is>
+          <t>6oaOMJCM</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="1" t="inlineStr">
+        <is>
+          <t>GtnFNGnI</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="1" t="inlineStr">
+        <is>
+          <t>Cl5MNy4F</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="1" t="inlineStr">
+        <is>
+          <t>ncdt7Da5</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
         <is>
           <t>3.25</t>
         </is>
       </c>
-      <c r="C779" t="inlineStr">
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="1" t="inlineStr">
+        <is>
+          <t>zVbm58Wj</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="1" t="inlineStr">
+        <is>
+          <t>ClkbRbmg</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="1" t="inlineStr">
+        <is>
+          <t>vyijTKIt</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="1" t="inlineStr">
+        <is>
+          <t>UiKMJ7op</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="1" t="inlineStr">
+        <is>
+          <t>fDIXAw3C</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="1" t="inlineStr">
+        <is>
+          <t>2wMu9HXO</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="1" t="inlineStr">
+        <is>
+          <t>EVz4aMcd</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="1" t="inlineStr">
+        <is>
+          <t>xfurRkgA</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="1" t="inlineStr">
+        <is>
+          <t>x8x5Vmef</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="1" t="inlineStr">
+        <is>
+          <t>d28hKstQ</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="1" t="inlineStr">
+        <is>
+          <t>4O1EPcZ2</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="1" t="inlineStr">
+        <is>
+          <t>r7UK2bLj</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="1" t="inlineStr">
+        <is>
+          <t>A7wjPTNM</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="1" t="inlineStr">
+        <is>
+          <t>MaxUHoGd</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="1" t="inlineStr">
+        <is>
+          <t>0GOk0Mlf</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="1" t="inlineStr">
+        <is>
+          <t>COwk8KcT</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="1" t="inlineStr">
+        <is>
+          <t>GdptAtTG</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="1" t="inlineStr">
+        <is>
+          <t>Cn4xUzKk</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="1" t="inlineStr">
+        <is>
+          <t>8Cpk5iUH</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr"/>
+      <c r="C805" t="inlineStr"/>
+      <c r="D805" t="inlineStr"/>
+    </row>
+    <row r="806">
+      <c r="A806" s="1" t="inlineStr">
+        <is>
+          <t>48L6dvlJ</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="1" t="inlineStr">
+        <is>
+          <t>QXQGEL3m</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="1" t="inlineStr">
+        <is>
+          <t>8GbVLFYR</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="1" t="inlineStr">
+        <is>
+          <t>zTovjLyo</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="1" t="inlineStr">
+        <is>
+          <t>O277Q1Dc</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
         <is>
           <t>3.20</t>
         </is>
       </c>
-      <c r="D779" t="inlineStr">
-        <is>
-          <t>2.25</t>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="1" t="inlineStr">
+        <is>
+          <t>YcUOCaYa</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="1" t="inlineStr">
+        <is>
+          <t>8Gr7PxI5</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="1" t="inlineStr">
+        <is>
+          <t>8tScb0J6</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="1" t="inlineStr">
+        <is>
+          <t>tSoZSBOc</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="1" t="inlineStr">
+        <is>
+          <t>fH65Tqom</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="1" t="inlineStr">
+        <is>
+          <t>0SlVn40n</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="1" t="inlineStr">
+        <is>
+          <t>bRdSS0FU</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="1" t="inlineStr">
+        <is>
+          <t>0UczBBw9</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>4.50</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D818"/>
+  <dimension ref="A1:D842"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11963,20 +11963,14 @@
           <t>fsjksfhd</t>
         </is>
       </c>
-      <c r="B780" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="C780" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D780" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="B780" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C780" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D780" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="781">
@@ -11985,20 +11979,14 @@
           <t>ltBAlx0M</t>
         </is>
       </c>
-      <c r="B781" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C781" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D781" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B781" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C781" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D781" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="782">
@@ -12007,20 +11995,14 @@
           <t>nywy5cp3</t>
         </is>
       </c>
-      <c r="B782" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="C782" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D782" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
+      <c r="B782" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C782" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D782" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="783">
@@ -12029,20 +12011,14 @@
           <t>6oaOMJCM</t>
         </is>
       </c>
-      <c r="B783" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
-      </c>
-      <c r="C783" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="D783" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
+      <c r="B783" t="n">
+        <v>10</v>
+      </c>
+      <c r="C783" t="n">
+        <v>7</v>
+      </c>
+      <c r="D783" t="n">
+        <v>1.18</v>
       </c>
     </row>
     <row r="784">
@@ -12051,20 +12027,14 @@
           <t>GtnFNGnI</t>
         </is>
       </c>
-      <c r="B784" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="C784" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D784" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
+      <c r="B784" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="C784" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D784" t="n">
+        <v>1.9</v>
       </c>
     </row>
     <row r="785">
@@ -12073,20 +12043,14 @@
           <t>Cl5MNy4F</t>
         </is>
       </c>
-      <c r="B785" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="C785" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D785" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B785" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C785" t="n">
+        <v>4</v>
+      </c>
+      <c r="D785" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="786">
@@ -12095,20 +12059,14 @@
           <t>ncdt7Da5</t>
         </is>
       </c>
-      <c r="B786" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C786" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D786" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B786" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C786" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D786" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="787">
@@ -12117,20 +12075,14 @@
           <t>zVbm58Wj</t>
         </is>
       </c>
-      <c r="B787" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C787" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D787" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="B787" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C787" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D787" t="n">
+        <v>2.55</v>
       </c>
     </row>
     <row r="788">
@@ -12139,20 +12091,14 @@
           <t>ClkbRbmg</t>
         </is>
       </c>
-      <c r="B788" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="C788" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="D788" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
+      <c r="B788" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C788" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D788" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="789">
@@ -12161,20 +12107,14 @@
           <t>vyijTKIt</t>
         </is>
       </c>
-      <c r="B789" t="inlineStr">
-        <is>
-          <t>9.50</t>
-        </is>
-      </c>
-      <c r="C789" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="D789" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
+      <c r="B789" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="C789" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D789" t="n">
+        <v>1.22</v>
       </c>
     </row>
     <row r="790">
@@ -12183,20 +12123,14 @@
           <t>UiKMJ7op</t>
         </is>
       </c>
-      <c r="B790" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="C790" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D790" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
+      <c r="B790" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C790" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D790" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="791">
@@ -12205,20 +12139,14 @@
           <t>fDIXAw3C</t>
         </is>
       </c>
-      <c r="B791" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="C791" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="D791" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
+      <c r="B791" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C791" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D791" t="n">
+        <v>5.75</v>
       </c>
     </row>
     <row r="792">
@@ -12227,20 +12155,14 @@
           <t>2wMu9HXO</t>
         </is>
       </c>
-      <c r="B792" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="C792" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D792" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
+      <c r="B792" t="n">
+        <v>6</v>
+      </c>
+      <c r="C792" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D792" t="n">
+        <v>1.38</v>
       </c>
     </row>
     <row r="793">
@@ -12249,20 +12171,14 @@
           <t>EVz4aMcd</t>
         </is>
       </c>
-      <c r="B793" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="C793" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D793" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
+      <c r="B793" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C793" t="n">
+        <v>4</v>
+      </c>
+      <c r="D793" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="794">
@@ -12271,20 +12187,14 @@
           <t>xfurRkgA</t>
         </is>
       </c>
-      <c r="B794" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="C794" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D794" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
+      <c r="B794" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C794" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D794" t="n">
+        <v>1.7</v>
       </c>
     </row>
     <row r="795">
@@ -12293,20 +12203,14 @@
           <t>x8x5Vmef</t>
         </is>
       </c>
-      <c r="B795" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C795" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D795" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="B795" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C795" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D795" t="n">
+        <v>3.25</v>
       </c>
     </row>
     <row r="796">
@@ -12315,20 +12219,14 @@
           <t>d28hKstQ</t>
         </is>
       </c>
-      <c r="B796" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="C796" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D796" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="B796" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C796" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D796" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="797">
@@ -12337,20 +12235,14 @@
           <t>4O1EPcZ2</t>
         </is>
       </c>
-      <c r="B797" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C797" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D797" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="B797" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C797" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D797" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="798">
@@ -12359,20 +12251,14 @@
           <t>r7UK2bLj</t>
         </is>
       </c>
-      <c r="B798" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="C798" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="D798" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
+      <c r="B798" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C798" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D798" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="799">
@@ -12381,20 +12267,14 @@
           <t>A7wjPTNM</t>
         </is>
       </c>
-      <c r="B799" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C799" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D799" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
+      <c r="B799" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C799" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D799" t="n">
+        <v>1.83</v>
       </c>
     </row>
     <row r="800">
@@ -12403,20 +12283,14 @@
           <t>MaxUHoGd</t>
         </is>
       </c>
-      <c r="B800" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C800" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D800" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
+      <c r="B800" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C800" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D800" t="n">
+        <v>2.63</v>
       </c>
     </row>
     <row r="801">
@@ -12425,20 +12299,14 @@
           <t>0GOk0Mlf</t>
         </is>
       </c>
-      <c r="B801" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C801" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D801" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="B801" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C801" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D801" t="n">
+        <v>3.25</v>
       </c>
     </row>
     <row r="802">
@@ -12447,20 +12315,14 @@
           <t>COwk8KcT</t>
         </is>
       </c>
-      <c r="B802" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="C802" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D802" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
+      <c r="B802" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C802" t="n">
+        <v>5</v>
+      </c>
+      <c r="D802" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="803">
@@ -12469,20 +12331,14 @@
           <t>GdptAtTG</t>
         </is>
       </c>
-      <c r="B803" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="C803" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D803" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="B803" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C803" t="n">
+        <v>4</v>
+      </c>
+      <c r="D803" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="804">
@@ -12491,20 +12347,14 @@
           <t>Cn4xUzKk</t>
         </is>
       </c>
-      <c r="B804" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="C804" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D804" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
+      <c r="B804" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C804" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D804" t="n">
+        <v>1.48</v>
       </c>
     </row>
     <row r="805">
@@ -12523,20 +12373,14 @@
           <t>48L6dvlJ</t>
         </is>
       </c>
-      <c r="B806" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C806" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D806" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B806" t="n">
+        <v>2</v>
+      </c>
+      <c r="C806" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D806" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="807">
@@ -12545,20 +12389,14 @@
           <t>QXQGEL3m</t>
         </is>
       </c>
-      <c r="B807" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C807" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D807" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B807" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C807" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D807" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="808">
@@ -12567,20 +12405,14 @@
           <t>8GbVLFYR</t>
         </is>
       </c>
-      <c r="B808" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="C808" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="D808" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
+      <c r="B808" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C808" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D808" t="n">
+        <v>1.45</v>
       </c>
     </row>
     <row r="809">
@@ -12589,20 +12421,14 @@
           <t>zTovjLyo</t>
         </is>
       </c>
-      <c r="B809" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C809" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D809" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="B809" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C809" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D809" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="810">
@@ -12611,20 +12437,14 @@
           <t>O277Q1Dc</t>
         </is>
       </c>
-      <c r="B810" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="C810" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D810" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="B810" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C810" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D810" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="811">
@@ -12633,20 +12453,14 @@
           <t>YcUOCaYa</t>
         </is>
       </c>
-      <c r="B811" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C811" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D811" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="B811" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C811" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D811" t="n">
+        <v>2.4</v>
       </c>
     </row>
     <row r="812">
@@ -12655,20 +12469,14 @@
           <t>8Gr7PxI5</t>
         </is>
       </c>
-      <c r="B812" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="C812" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D812" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
+      <c r="B812" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C812" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D812" t="n">
+        <v>1.62</v>
       </c>
     </row>
     <row r="813">
@@ -12677,20 +12485,14 @@
           <t>8tScb0J6</t>
         </is>
       </c>
-      <c r="B813" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="C813" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D813" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="B813" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C813" t="n">
+        <v>4</v>
+      </c>
+      <c r="D813" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="814">
@@ -12699,20 +12501,14 @@
           <t>tSoZSBOc</t>
         </is>
       </c>
-      <c r="B814" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C814" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D814" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B814" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C814" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D814" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="815">
@@ -12721,20 +12517,14 @@
           <t>fH65Tqom</t>
         </is>
       </c>
-      <c r="B815" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="C815" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D815" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
+      <c r="B815" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C815" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D815" t="n">
+        <v>1.42</v>
       </c>
     </row>
     <row r="816">
@@ -12743,20 +12533,14 @@
           <t>0SlVn40n</t>
         </is>
       </c>
-      <c r="B816" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="C816" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="D816" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
+      <c r="B816" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C816" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D816" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="817">
@@ -12765,20 +12549,14 @@
           <t>bRdSS0FU</t>
         </is>
       </c>
-      <c r="B817" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="C817" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D817" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
+      <c r="B817" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C817" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D817" t="n">
+        <v>5.75</v>
       </c>
     </row>
     <row r="818">
@@ -12787,19 +12565,541 @@
           <t>0UczBBw9</t>
         </is>
       </c>
-      <c r="B818" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C818" t="inlineStr">
+      <c r="B818" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C818" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D818" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="1" t="inlineStr">
+        <is>
+          <t>ShJjaSDs</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="1" t="inlineStr">
+        <is>
+          <t>Y5lic6rf</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="1" t="inlineStr">
+        <is>
+          <t>tWiaepD6</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="1" t="inlineStr">
+        <is>
+          <t>UiYgHRZP</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="1" t="inlineStr">
+        <is>
+          <t>n9EQB5cm</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="1" t="inlineStr">
+        <is>
+          <t>Gl6s8NdC</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="1" t="inlineStr">
+        <is>
+          <t>OE9k61RO</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="1" t="inlineStr">
+        <is>
+          <t>EJfDwuEj</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="1" t="inlineStr">
+        <is>
+          <t>p44sq1jT</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="1" t="inlineStr">
+        <is>
+          <t>8EJl8jJs</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="1" t="inlineStr">
+        <is>
+          <t>dtgtsEKr</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="1" t="inlineStr">
+        <is>
+          <t>2uy8aMzA</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="1" t="inlineStr">
+        <is>
+          <t>fFXa1r6c</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="1" t="inlineStr">
+        <is>
+          <t>hSxF3TVr</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="1" t="inlineStr">
+        <is>
+          <t>0QDzm8zG</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="1" t="inlineStr">
+        <is>
+          <t>6Pu8UaKl</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="1" t="inlineStr">
+        <is>
+          <t>jD19YTxK</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="1" t="inlineStr">
+        <is>
+          <t>nqmuT70s</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="1" t="inlineStr">
+        <is>
+          <t>rBtlRoVg</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="1" t="inlineStr">
+        <is>
+          <t>CUhG170e</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="1" t="inlineStr">
+        <is>
+          <t>fDrzkU53</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="1" t="inlineStr">
+        <is>
+          <t>SvUGSwk1</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
         <is>
           <t>3.90</t>
         </is>
       </c>
-      <c r="D818" t="inlineStr">
-        <is>
-          <t>4.50</t>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="1" t="inlineStr">
+        <is>
+          <t>z5XOQHJD</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="1" t="inlineStr">
+        <is>
+          <t>2JelRQDd</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>3.90</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D842"/>
+  <dimension ref="A1:D845"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12581,20 +12581,14 @@
           <t>ShJjaSDs</t>
         </is>
       </c>
-      <c r="B819" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="C819" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D819" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
+      <c r="B819" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C819" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D819" t="n">
+        <v>1.75</v>
       </c>
     </row>
     <row r="820">
@@ -12603,20 +12597,14 @@
           <t>Y5lic6rf</t>
         </is>
       </c>
-      <c r="B820" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C820" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D820" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="B820" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C820" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D820" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="821">
@@ -12625,20 +12613,14 @@
           <t>tWiaepD6</t>
         </is>
       </c>
-      <c r="B821" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="C821" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D821" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="B821" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C821" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D821" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="822">
@@ -12647,20 +12629,14 @@
           <t>UiYgHRZP</t>
         </is>
       </c>
-      <c r="B822" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="C822" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D822" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B822" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C822" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D822" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="823">
@@ -12669,20 +12645,14 @@
           <t>n9EQB5cm</t>
         </is>
       </c>
-      <c r="B823" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C823" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D823" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="B823" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C823" t="n">
+        <v>4</v>
+      </c>
+      <c r="D823" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="824">
@@ -12691,20 +12661,14 @@
           <t>Gl6s8NdC</t>
         </is>
       </c>
-      <c r="B824" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C824" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D824" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="B824" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C824" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D824" t="n">
+        <v>3.25</v>
       </c>
     </row>
     <row r="825">
@@ -12713,20 +12677,14 @@
           <t>OE9k61RO</t>
         </is>
       </c>
-      <c r="B825" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="C825" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="D825" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
+      <c r="B825" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C825" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D825" t="n">
+        <v>5.75</v>
       </c>
     </row>
     <row r="826">
@@ -12735,20 +12693,14 @@
           <t>EJfDwuEj</t>
         </is>
       </c>
-      <c r="B826" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="C826" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D826" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B826" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C826" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D826" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="827">
@@ -12757,20 +12709,14 @@
           <t>p44sq1jT</t>
         </is>
       </c>
-      <c r="B827" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C827" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D827" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="B827" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C827" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D827" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="828">
@@ -12779,20 +12725,14 @@
           <t>8EJl8jJs</t>
         </is>
       </c>
-      <c r="B828" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="C828" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-      <c r="D828" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
+      <c r="B828" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="C828" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D828" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="829">
@@ -12801,20 +12741,14 @@
           <t>dtgtsEKr</t>
         </is>
       </c>
-      <c r="B829" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="C829" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D829" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
+      <c r="B829" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C829" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D829" t="n">
+        <v>6.25</v>
       </c>
     </row>
     <row r="830">
@@ -12823,20 +12757,14 @@
           <t>2uy8aMzA</t>
         </is>
       </c>
-      <c r="B830" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C830" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="D830" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B830" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C830" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="D830" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="831">
@@ -12845,20 +12773,14 @@
           <t>fFXa1r6c</t>
         </is>
       </c>
-      <c r="B831" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C831" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D831" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="B831" t="n">
+        <v>2</v>
+      </c>
+      <c r="C831" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D831" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="832">
@@ -12867,20 +12789,14 @@
           <t>hSxF3TVr</t>
         </is>
       </c>
-      <c r="B832" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C832" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D832" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="B832" t="n">
+        <v>2</v>
+      </c>
+      <c r="C832" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D832" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="833">
@@ -12889,20 +12805,14 @@
           <t>0QDzm8zG</t>
         </is>
       </c>
-      <c r="B833" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="C833" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D833" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B833" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C833" t="n">
+        <v>4</v>
+      </c>
+      <c r="D833" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="834">
@@ -12911,20 +12821,14 @@
           <t>6Pu8UaKl</t>
         </is>
       </c>
-      <c r="B834" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C834" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D834" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="B834" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C834" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D834" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="835">
@@ -12933,20 +12837,14 @@
           <t>jD19YTxK</t>
         </is>
       </c>
-      <c r="B835" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C835" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D835" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
+      <c r="B835" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C835" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D835" t="n">
+        <v>4.1</v>
       </c>
     </row>
     <row r="836">
@@ -12955,20 +12853,14 @@
           <t>nqmuT70s</t>
         </is>
       </c>
-      <c r="B836" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C836" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D836" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="B836" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C836" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D836" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="837">
@@ -12977,20 +12869,14 @@
           <t>rBtlRoVg</t>
         </is>
       </c>
-      <c r="B837" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C837" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D837" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="B837" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C837" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D837" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="838">
@@ -12999,20 +12885,14 @@
           <t>CUhG170e</t>
         </is>
       </c>
-      <c r="B838" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C838" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D838" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="B838" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C838" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D838" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="839">
@@ -13021,20 +12901,14 @@
           <t>fDrzkU53</t>
         </is>
       </c>
-      <c r="B839" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C839" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D839" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
+      <c r="B839" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C839" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D839" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="840">
@@ -13043,20 +12917,14 @@
           <t>SvUGSwk1</t>
         </is>
       </c>
-      <c r="B840" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="C840" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D840" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
+      <c r="B840" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C840" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D840" t="n">
+        <v>1.95</v>
       </c>
     </row>
     <row r="841">
@@ -13065,20 +12933,14 @@
           <t>z5XOQHJD</t>
         </is>
       </c>
-      <c r="B841" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C841" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D841" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="B841" t="n">
+        <v>3</v>
+      </c>
+      <c r="C841" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D841" t="n">
+        <v>2.35</v>
       </c>
     </row>
     <row r="842">
@@ -13087,19 +12949,79 @@
           <t>2JelRQDd</t>
         </is>
       </c>
-      <c r="B842" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C842" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D842" t="inlineStr">
-        <is>
-          <t>3.90</t>
+      <c r="B842" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C842" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D842" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="1" t="inlineStr">
+        <is>
+          <t>2ot8gOsJ</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="1" t="inlineStr">
+        <is>
+          <t>SSZaQ4Ct</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="1" t="inlineStr">
+        <is>
+          <t>6i2uTnqp</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>2.38</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D845"/>
+  <dimension ref="A1:D858"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12965,20 +12965,14 @@
           <t>2ot8gOsJ</t>
         </is>
       </c>
-      <c r="B843" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C843" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D843" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="B843" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C843" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D843" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="844">
@@ -12987,20 +12981,14 @@
           <t>SSZaQ4Ct</t>
         </is>
       </c>
-      <c r="B844" t="inlineStr">
-        <is>
-          <t>8.50</t>
-        </is>
-      </c>
-      <c r="C844" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="D844" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
+      <c r="B844" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C844" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D844" t="n">
+        <v>1.33</v>
       </c>
     </row>
     <row r="845">
@@ -13009,19 +12997,299 @@
           <t>6i2uTnqp</t>
         </is>
       </c>
-      <c r="B845" t="inlineStr">
+      <c r="B845" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C845" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D845" t="n">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="1" t="inlineStr">
+        <is>
+          <t>KMCY9qSa</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="1" t="inlineStr">
+        <is>
+          <t>Aau4hOTh</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="1" t="inlineStr">
+        <is>
+          <t>bLBozsEO</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="1" t="inlineStr">
+        <is>
+          <t>jypdPPa6</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="1" t="inlineStr">
+        <is>
+          <t>2Zydfpat</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
         <is>
           <t>2.88</t>
         </is>
       </c>
-      <c r="C845" t="inlineStr">
+    </row>
+    <row r="851">
+      <c r="A851" s="1" t="inlineStr">
+        <is>
+          <t>6RYCj2b5</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="1" t="inlineStr">
+        <is>
+          <t>Ao0VwPEa</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="1" t="inlineStr">
+        <is>
+          <t>KfdOaoV7</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="1" t="inlineStr">
+        <is>
+          <t>CjY4N3UI</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="1" t="inlineStr">
+        <is>
+          <t>ImLjo7MP</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="1" t="inlineStr">
+        <is>
+          <t>xY1Nuopm</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="1" t="inlineStr">
+        <is>
+          <t>0jZANlNE</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
         <is>
           <t>3.40</t>
         </is>
       </c>
-      <c r="D845" t="inlineStr">
-        <is>
-          <t>2.38</t>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="1" t="inlineStr">
+        <is>
+          <t>6Dgvx3qC</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>3.10</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D858"/>
+  <dimension ref="A1:D880"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13013,20 +13013,14 @@
           <t>KMCY9qSa</t>
         </is>
       </c>
-      <c r="B846" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C846" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D846" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B846" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C846" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D846" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="847">
@@ -13035,20 +13029,14 @@
           <t>Aau4hOTh</t>
         </is>
       </c>
-      <c r="B847" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="C847" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D847" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
+      <c r="B847" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C847" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D847" t="n">
+        <v>3.75</v>
       </c>
     </row>
     <row r="848">
@@ -13057,20 +13045,14 @@
           <t>bLBozsEO</t>
         </is>
       </c>
-      <c r="B848" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C848" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D848" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="B848" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C848" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D848" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="849">
@@ -13079,20 +13061,14 @@
           <t>jypdPPa6</t>
         </is>
       </c>
-      <c r="B849" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C849" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D849" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="B849" t="n">
+        <v>3</v>
+      </c>
+      <c r="C849" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D849" t="n">
+        <v>2.35</v>
       </c>
     </row>
     <row r="850">
@@ -13101,20 +13077,14 @@
           <t>2Zydfpat</t>
         </is>
       </c>
-      <c r="B850" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C850" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D850" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
+      <c r="B850" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C850" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D850" t="n">
+        <v>2.88</v>
       </c>
     </row>
     <row r="851">
@@ -13123,20 +13093,14 @@
           <t>6RYCj2b5</t>
         </is>
       </c>
-      <c r="B851" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C851" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D851" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B851" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C851" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D851" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="852">
@@ -13145,20 +13109,14 @@
           <t>Ao0VwPEa</t>
         </is>
       </c>
-      <c r="B852" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="C852" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D852" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="B852" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C852" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D852" t="n">
+        <v>2.45</v>
       </c>
     </row>
     <row r="853">
@@ -13167,20 +13125,14 @@
           <t>KfdOaoV7</t>
         </is>
       </c>
-      <c r="B853" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C853" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D853" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="B853" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C853" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D853" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="854">
@@ -13189,20 +13141,14 @@
           <t>CjY4N3UI</t>
         </is>
       </c>
-      <c r="B854" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="C854" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D854" t="inlineStr">
-        <is>
-          <t>9.50</t>
-        </is>
+      <c r="B854" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C854" t="n">
+        <v>5</v>
+      </c>
+      <c r="D854" t="n">
+        <v>9.5</v>
       </c>
     </row>
     <row r="855">
@@ -13211,20 +13157,14 @@
           <t>ImLjo7MP</t>
         </is>
       </c>
-      <c r="B855" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C855" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D855" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="B855" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C855" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D855" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="856">
@@ -13233,20 +13173,14 @@
           <t>xY1Nuopm</t>
         </is>
       </c>
-      <c r="B856" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C856" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D856" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="B856" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C856" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D856" t="n">
+        <v>2.55</v>
       </c>
     </row>
     <row r="857">
@@ -13255,20 +13189,14 @@
           <t>0jZANlNE</t>
         </is>
       </c>
-      <c r="B857" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C857" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D857" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="B857" t="n">
+        <v>2</v>
+      </c>
+      <c r="C857" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D857" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="858">
@@ -13277,19 +13205,395 @@
           <t>6Dgvx3qC</t>
         </is>
       </c>
-      <c r="B858" t="inlineStr">
+      <c r="B858" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C858" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D858" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="1" t="inlineStr">
+        <is>
+          <t>rw5cZaeB</t>
+        </is>
+      </c>
+      <c r="B859" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C859" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D859" t="n">
+        <v>2.63</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="1" t="inlineStr">
+        <is>
+          <t>ABRGMMB5</t>
+        </is>
+      </c>
+      <c r="B860" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C860" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D860" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="1" t="inlineStr">
+        <is>
+          <t>rPPOK0tI</t>
+        </is>
+      </c>
+      <c r="B861" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C861" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D861" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="1" t="inlineStr">
+        <is>
+          <t>viJXIvBU</t>
+        </is>
+      </c>
+      <c r="B862" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C862" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D862" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="1" t="inlineStr">
+        <is>
+          <t>zypxSHmo</t>
+        </is>
+      </c>
+      <c r="B863" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="C863" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D863" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="1" t="inlineStr">
+        <is>
+          <t>v5b6XwQN</t>
+        </is>
+      </c>
+      <c r="B864" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C864" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D864" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="1" t="inlineStr">
+        <is>
+          <t>bsmMnKcU</t>
+        </is>
+      </c>
+      <c r="B865" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C865" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D865" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="1" t="inlineStr">
+        <is>
+          <t>ALGv51Db</t>
+        </is>
+      </c>
+      <c r="B866" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C866" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D866" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="1" t="inlineStr">
+        <is>
+          <t>AJyLpXRq</t>
+        </is>
+      </c>
+      <c r="B867" t="n">
+        <v>3</v>
+      </c>
+      <c r="C867" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D867" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="1" t="inlineStr">
+        <is>
+          <t>buIF6El3</t>
+        </is>
+      </c>
+      <c r="B868" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C868" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D868" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="1" t="inlineStr">
+        <is>
+          <t>65LN4hJF</t>
+        </is>
+      </c>
+      <c r="B869" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C869" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D869" t="n">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="1" t="inlineStr">
+        <is>
+          <t>6k1r5t7m</t>
+        </is>
+      </c>
+      <c r="B870" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C870" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D870" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="1" t="inlineStr">
+        <is>
+          <t>0lfi3Ky0</t>
+        </is>
+      </c>
+      <c r="B871" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C871" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D871" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="1" t="inlineStr">
+        <is>
+          <t>vuXKltTH</t>
+        </is>
+      </c>
+      <c r="B872" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C872" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D872" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="1" t="inlineStr">
+        <is>
+          <t>l6SV6Nrn</t>
+        </is>
+      </c>
+      <c r="B873" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C873" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D873" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="1" t="inlineStr">
+        <is>
+          <t>SK9W2WmS</t>
+        </is>
+      </c>
+      <c r="B874" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C874" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D874" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="1" t="inlineStr">
+        <is>
+          <t>rXZSrBdd</t>
+        </is>
+      </c>
+      <c r="B875" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C875" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D875" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="1" t="inlineStr">
+        <is>
+          <t>EqY7Orsg</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
         <is>
           <t>2.20</t>
         </is>
       </c>
-      <c r="C858" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D858" t="inlineStr">
-        <is>
-          <t>3.10</t>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="1" t="inlineStr">
+        <is>
+          <t>EcDtwrdn</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="1" t="inlineStr">
+        <is>
+          <t>zD1kyMQb</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="1" t="inlineStr">
+        <is>
+          <t>EJlHkLuh</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="1" t="inlineStr">
+        <is>
+          <t>IoKn3urB</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>2.45</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D880"/>
+  <dimension ref="A1:D888"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13493,20 +13493,14 @@
           <t>EqY7Orsg</t>
         </is>
       </c>
-      <c r="B876" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C876" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D876" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="B876" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C876" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D876" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="877">
@@ -13515,20 +13509,14 @@
           <t>EcDtwrdn</t>
         </is>
       </c>
-      <c r="B877" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C877" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D877" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="B877" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C877" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D877" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="878">
@@ -13537,20 +13525,14 @@
           <t>zD1kyMQb</t>
         </is>
       </c>
-      <c r="B878" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="C878" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D878" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
+      <c r="B878" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C878" t="n">
+        <v>4</v>
+      </c>
+      <c r="D878" t="n">
+        <v>1.91</v>
       </c>
     </row>
     <row r="879">
@@ -13559,20 +13541,14 @@
           <t>EJlHkLuh</t>
         </is>
       </c>
-      <c r="B879" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="C879" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D879" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="B879" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C879" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D879" t="n">
+        <v>2.1</v>
       </c>
     </row>
     <row r="880">
@@ -13581,19 +13557,189 @@
           <t>IoKn3urB</t>
         </is>
       </c>
-      <c r="B880" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C880" t="inlineStr">
+      <c r="B880" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C880" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D880" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="1" t="inlineStr">
+        <is>
+          <t>vmNvRnvg</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="1" t="inlineStr">
+        <is>
+          <t>8SEeN4wI</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
         <is>
           <t>3.30</t>
         </is>
       </c>
-      <c r="D880" t="inlineStr">
-        <is>
-          <t>2.45</t>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="1" t="inlineStr">
+        <is>
+          <t>86wLARgC</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="1" t="inlineStr">
+        <is>
+          <t>rqnYB2b4</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="1" t="inlineStr">
+        <is>
+          <t>nDQnPQ85</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="1" t="inlineStr">
+        <is>
+          <t>4YWT85OO</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="1" t="inlineStr">
+        <is>
+          <t>Kp7wT89t</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="1" t="inlineStr">
+        <is>
+          <t>0tzDCmPa</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>10.00</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D888"/>
+  <dimension ref="A1:D950"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13573,20 +13573,14 @@
           <t>vmNvRnvg</t>
         </is>
       </c>
-      <c r="B881" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C881" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D881" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
+      <c r="B881" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C881" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D881" t="n">
+        <v>2.88</v>
       </c>
     </row>
     <row r="882">
@@ -13595,20 +13589,14 @@
           <t>8SEeN4wI</t>
         </is>
       </c>
-      <c r="B882" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C882" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D882" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="B882" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C882" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D882" t="n">
+        <v>2.75</v>
       </c>
     </row>
     <row r="883">
@@ -13617,20 +13605,14 @@
           <t>86wLARgC</t>
         </is>
       </c>
-      <c r="B883" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="C883" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="D883" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
+      <c r="B883" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C883" t="n">
+        <v>6</v>
+      </c>
+      <c r="D883" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="884">
@@ -13639,20 +13621,14 @@
           <t>rqnYB2b4</t>
         </is>
       </c>
-      <c r="B884" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C884" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D884" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B884" t="n">
+        <v>2</v>
+      </c>
+      <c r="C884" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D884" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="885">
@@ -13661,20 +13637,14 @@
           <t>nDQnPQ85</t>
         </is>
       </c>
-      <c r="B885" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
-      </c>
-      <c r="C885" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="D885" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
+      <c r="B885" t="n">
+        <v>11</v>
+      </c>
+      <c r="C885" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D885" t="n">
+        <v>1.29</v>
       </c>
     </row>
     <row r="886">
@@ -13683,20 +13653,14 @@
           <t>4YWT85OO</t>
         </is>
       </c>
-      <c r="B886" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C886" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D886" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="B886" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C886" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D886" t="n">
+        <v>2.2</v>
       </c>
     </row>
     <row r="887">
@@ -13705,20 +13669,14 @@
           <t>Kp7wT89t</t>
         </is>
       </c>
-      <c r="B887" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="C887" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="D887" t="inlineStr">
-        <is>
-          <t>13.00</t>
-        </is>
+      <c r="B887" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="C887" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D887" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="888">
@@ -13727,19 +13685,1017 @@
           <t>0tzDCmPa</t>
         </is>
       </c>
-      <c r="B888" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="C888" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-      <c r="D888" t="inlineStr">
-        <is>
-          <t>10.00</t>
+      <c r="B888" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C888" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="D888" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="1" t="inlineStr">
+        <is>
+          <t>zil0kCo9</t>
+        </is>
+      </c>
+      <c r="B889" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C889" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D889" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="1" t="inlineStr">
+        <is>
+          <t>drzevnw8</t>
+        </is>
+      </c>
+      <c r="B890" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C890" t="n">
+        <v>4</v>
+      </c>
+      <c r="D890" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="1" t="inlineStr">
+        <is>
+          <t>EJ4unbdE</t>
+        </is>
+      </c>
+      <c r="B891" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C891" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D891" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="1" t="inlineStr">
+        <is>
+          <t>MqhPmaA4</t>
+        </is>
+      </c>
+      <c r="B892" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="C892" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D892" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="1" t="inlineStr">
+        <is>
+          <t>lb85TUOk</t>
+        </is>
+      </c>
+      <c r="B893" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C893" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D893" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="1" t="inlineStr">
+        <is>
+          <t>rc1ER8g2</t>
+        </is>
+      </c>
+      <c r="B894" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C894" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D894" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="1" t="inlineStr">
+        <is>
+          <t>21YvrUwq</t>
+        </is>
+      </c>
+      <c r="B895" t="n">
+        <v>2</v>
+      </c>
+      <c r="C895" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D895" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="1" t="inlineStr">
+        <is>
+          <t>OGMmt88e</t>
+        </is>
+      </c>
+      <c r="B896" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C896" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D896" t="n">
+        <v>2.63</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="1" t="inlineStr">
+        <is>
+          <t>WIs9mjGL</t>
+        </is>
+      </c>
+      <c r="B897" t="n">
+        <v>4</v>
+      </c>
+      <c r="C897" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D897" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="1" t="inlineStr">
+        <is>
+          <t>KGBXrvkg</t>
+        </is>
+      </c>
+      <c r="B898" t="n">
+        <v>7</v>
+      </c>
+      <c r="C898" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D898" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="1" t="inlineStr">
+        <is>
+          <t>dzjtswy3</t>
+        </is>
+      </c>
+      <c r="B899" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C899" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D899" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="1" t="inlineStr">
+        <is>
+          <t>pYDbcw4n</t>
+        </is>
+      </c>
+      <c r="B900" t="n">
+        <v>8</v>
+      </c>
+      <c r="C900" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D900" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="1" t="inlineStr">
+        <is>
+          <t>numxPqbK</t>
+        </is>
+      </c>
+      <c r="B901" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C901" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D901" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="1" t="inlineStr">
+        <is>
+          <t>jergPhh3</t>
+        </is>
+      </c>
+      <c r="B902" t="n">
+        <v>10</v>
+      </c>
+      <c r="C902" t="n">
+        <v>7</v>
+      </c>
+      <c r="D902" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="1" t="inlineStr">
+        <is>
+          <t>CleRAgwA</t>
+        </is>
+      </c>
+      <c r="B903" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="C903" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="D903" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="1" t="inlineStr">
+        <is>
+          <t>vcjbUvz0</t>
+        </is>
+      </c>
+      <c r="B904" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C904" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D904" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="1" t="inlineStr">
+        <is>
+          <t>QXl3HMlJ</t>
+        </is>
+      </c>
+      <c r="B905" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C905" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D905" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="1" t="inlineStr">
+        <is>
+          <t>MLJXDJkJ</t>
+        </is>
+      </c>
+      <c r="B906" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="C906" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D906" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="1" t="inlineStr">
+        <is>
+          <t>bJ6s32y1</t>
+        </is>
+      </c>
+      <c r="B907" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C907" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D907" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="1" t="inlineStr">
+        <is>
+          <t>Olj71k0d</t>
+        </is>
+      </c>
+      <c r="B908" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C908" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D908" t="n">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="1" t="inlineStr">
+        <is>
+          <t>f9YlwzJU</t>
+        </is>
+      </c>
+      <c r="B909" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C909" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D909" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="1" t="inlineStr">
+        <is>
+          <t>CAW1NWMF</t>
+        </is>
+      </c>
+      <c r="B910" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="C910" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D910" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="1" t="inlineStr">
+        <is>
+          <t>I9bZ4O6l</t>
+        </is>
+      </c>
+      <c r="B911" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C911" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D911" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="1" t="inlineStr">
+        <is>
+          <t>4nz63BVq</t>
+        </is>
+      </c>
+      <c r="B912" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C912" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D912" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="1" t="inlineStr">
+        <is>
+          <t>QTtYtIJ5</t>
+        </is>
+      </c>
+      <c r="B913" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C913" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D913" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="1" t="inlineStr">
+        <is>
+          <t>4OiJCF8c</t>
+        </is>
+      </c>
+      <c r="B914" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C914" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D914" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="1" t="inlineStr">
+        <is>
+          <t>4O9xWL3C</t>
+        </is>
+      </c>
+      <c r="B915" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C915" t="n">
+        <v>4</v>
+      </c>
+      <c r="D915" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="1" t="inlineStr">
+        <is>
+          <t>xCILZ34m</t>
+        </is>
+      </c>
+      <c r="B916" t="n">
+        <v>3</v>
+      </c>
+      <c r="C916" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D916" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="1" t="inlineStr">
+        <is>
+          <t>EBQeZQHd</t>
+        </is>
+      </c>
+      <c r="B917" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C917" t="n">
+        <v>4</v>
+      </c>
+      <c r="D917" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="1" t="inlineStr">
+        <is>
+          <t>OSEWlCGj</t>
+        </is>
+      </c>
+      <c r="B918" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C918" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D918" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="1" t="inlineStr">
+        <is>
+          <t>0Cv7SI4C</t>
+        </is>
+      </c>
+      <c r="B919" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C919" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D919" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="1" t="inlineStr">
+        <is>
+          <t>6oNmymmp</t>
+        </is>
+      </c>
+      <c r="B920" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C920" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D920" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="1" t="inlineStr">
+        <is>
+          <t>boVidfOG</t>
+        </is>
+      </c>
+      <c r="B921" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="C921" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D921" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="1" t="inlineStr">
+        <is>
+          <t>U5efJrK6</t>
+        </is>
+      </c>
+      <c r="B922" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C922" t="n">
+        <v>4</v>
+      </c>
+      <c r="D922" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="1" t="inlineStr">
+        <is>
+          <t>WW4k1t6D</t>
+        </is>
+      </c>
+      <c r="B923" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C923" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D923" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="1" t="inlineStr">
+        <is>
+          <t>IRykuQtQ</t>
+        </is>
+      </c>
+      <c r="B924" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C924" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D924" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="1" t="inlineStr">
+        <is>
+          <t>vX67eHYb</t>
+        </is>
+      </c>
+      <c r="B925" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C925" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D925" t="n">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="1" t="inlineStr">
+        <is>
+          <t>INw8JNLs</t>
+        </is>
+      </c>
+      <c r="B926" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C926" t="n">
+        <v>7</v>
+      </c>
+      <c r="D926" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="1" t="inlineStr">
+        <is>
+          <t>8Glz9X7M</t>
+        </is>
+      </c>
+      <c r="B927" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C927" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D927" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="1" t="inlineStr">
+        <is>
+          <t>QgQOFuL6</t>
+        </is>
+      </c>
+      <c r="B928" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C928" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D928" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="1" t="inlineStr">
+        <is>
+          <t>8xrFQdZO</t>
+        </is>
+      </c>
+      <c r="B929" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C929" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D929" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="1" t="inlineStr">
+        <is>
+          <t>EF6JyNsQ</t>
+        </is>
+      </c>
+      <c r="B930" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C930" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D930" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="1" t="inlineStr">
+        <is>
+          <t>rilluH5F</t>
+        </is>
+      </c>
+      <c r="B931" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C931" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D931" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="1" t="inlineStr">
+        <is>
+          <t>YamjW05m</t>
+        </is>
+      </c>
+      <c r="B932" t="n">
+        <v>3</v>
+      </c>
+      <c r="C932" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D932" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="1" t="inlineStr">
+        <is>
+          <t>Cp5Fge3B</t>
+        </is>
+      </c>
+      <c r="B933" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C933" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D933" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="1" t="inlineStr">
+        <is>
+          <t>fDO0fYhT</t>
+        </is>
+      </c>
+      <c r="B934" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C934" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D934" t="n">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="1" t="inlineStr">
+        <is>
+          <t>n3DPp0Kt</t>
+        </is>
+      </c>
+      <c r="B935" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="C935" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D935" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="1" t="inlineStr">
+        <is>
+          <t>YgptudlI</t>
+        </is>
+      </c>
+      <c r="B936" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C936" t="n">
+        <v>5</v>
+      </c>
+      <c r="D936" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="1" t="inlineStr">
+        <is>
+          <t>bNOqAmee</t>
+        </is>
+      </c>
+      <c r="B937" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C937" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D937" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="1" t="inlineStr">
+        <is>
+          <t>Y1ha1b6C</t>
+        </is>
+      </c>
+      <c r="B938" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C938" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D938" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="1" t="inlineStr">
+        <is>
+          <t>KW3Aelt2</t>
+        </is>
+      </c>
+      <c r="B939" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C939" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D939" t="n">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="1" t="inlineStr">
+        <is>
+          <t>CQjdJiY8</t>
+        </is>
+      </c>
+      <c r="B940" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="C940" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D940" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="1" t="inlineStr">
+        <is>
+          <t>x8zyC9Qr</t>
+        </is>
+      </c>
+      <c r="B941" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C941" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D941" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="1" t="inlineStr">
+        <is>
+          <t>6mSi8RP7</t>
+        </is>
+      </c>
+      <c r="B942" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C942" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D942" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="1" t="inlineStr">
+        <is>
+          <t>MeAvWUHE</t>
+        </is>
+      </c>
+      <c r="B943" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C943" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D943" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="1" t="inlineStr">
+        <is>
+          <t>f98nU8nR</t>
+        </is>
+      </c>
+      <c r="B944" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C944" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D944" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="1" t="inlineStr">
+        <is>
+          <t>O4A1cABk</t>
+        </is>
+      </c>
+      <c r="B945" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C945" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D945" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="1" t="inlineStr">
+        <is>
+          <t>UTo8axyP</t>
+        </is>
+      </c>
+      <c r="B946" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C946" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D946" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="1" t="inlineStr">
+        <is>
+          <t>xUBBOnAl</t>
+        </is>
+      </c>
+      <c r="B947" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C947" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D947" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="1" t="inlineStr">
+        <is>
+          <t>8hp5HV2L</t>
+        </is>
+      </c>
+      <c r="B948" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C948" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D948" t="n">
+        <v>2.63</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="1" t="inlineStr">
+        <is>
+          <t>ratYowuH</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="1" t="inlineStr">
+        <is>
+          <t>vwSGH1jf</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>1.33</t>
         </is>
       </c>
     </row>
